--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,12 +427,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC5"/>
+  <dimension ref="A1:AC17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="25" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -632,36 +632,32 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>07:34</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr"/>
       <c r="K2" s="2" t="inlineStr"/>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
-        </is>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr"/>
       <c r="N2" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -669,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -693,37 +689,33 @@
       </c>
       <c r="W2" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X2" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y2" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr">
-        <is>
-          <t>84.0</t>
-        </is>
-      </c>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>1/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -784,7 +776,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +826,7 @@
       <c r="AB3" s="2" t="inlineStr"/>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -895,7 +887,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -945,7 +937,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
         </is>
       </c>
     </row>
@@ -953,22 +945,22 @@
       <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>沪A56630D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>06:40</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>06:50</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1001,12 +993,12 @@
       <c r="M5" s="2" t="inlineStr"/>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>06:20</t>
+          <t>07:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1020,7 +1012,7 @@
       <c r="T5" s="2" t="inlineStr"/>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:40</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
@@ -1056,7 +1048,1339 @@
       <c r="AB5" s="2" t="inlineStr"/>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/4</t>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr"/>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+      <c r="S6" s="2" t="inlineStr"/>
+      <c r="T6" s="2" t="inlineStr"/>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X6" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y6" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr"/>
+      <c r="AC6" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr"/>
+      <c r="K7" s="2" t="inlineStr"/>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+      <c r="S7" s="2" t="inlineStr"/>
+      <c r="T7" s="2" t="inlineStr"/>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X7" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y7" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z7" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AC7" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr"/>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
+      <c r="R8" s="2" t="inlineStr"/>
+      <c r="S8" s="2" t="inlineStr"/>
+      <c r="T8" s="2" t="inlineStr"/>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X8" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y8" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AC8" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
+      <c r="K9" s="2" t="inlineStr"/>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr"/>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+      <c r="S9" s="2" t="inlineStr"/>
+      <c r="T9" s="2" t="inlineStr"/>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>07:00</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X9" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y9" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr"/>
+      <c r="AC9" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr"/>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
+      <c r="K10" s="2" t="inlineStr"/>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr"/>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+      <c r="S10" s="2" t="inlineStr"/>
+      <c r="T10" s="2" t="inlineStr"/>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>07:10</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X10" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y10" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AC10" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr"/>
+      <c r="K11" s="2" t="inlineStr"/>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr"/>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+      <c r="S11" s="2" t="inlineStr"/>
+      <c r="T11" s="2" t="inlineStr"/>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>07:15</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X11" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y11" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr"/>
+      <c r="AC11" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr"/>
+      <c r="K12" s="2" t="inlineStr"/>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P12" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr"/>
+      <c r="R12" s="2" t="inlineStr"/>
+      <c r="S12" s="2" t="inlineStr"/>
+      <c r="T12" s="2" t="inlineStr"/>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X12" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y12" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AC12" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr"/>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr"/>
+      <c r="K13" s="2" t="inlineStr"/>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr"/>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr"/>
+      <c r="R13" s="2" t="inlineStr"/>
+      <c r="S13" s="2" t="inlineStr"/>
+      <c r="T13" s="2" t="inlineStr"/>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W13" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X13" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y13" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AC13" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr"/>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr"/>
+      <c r="R14" s="2" t="inlineStr"/>
+      <c r="S14" s="2" t="inlineStr"/>
+      <c r="T14" s="2" t="inlineStr"/>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W14" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X14" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y14" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr"/>
+      <c r="AC14" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr"/>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr"/>
+      <c r="K15" s="2" t="inlineStr"/>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr"/>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O15" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P15" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="R15" s="2" t="inlineStr"/>
+      <c r="S15" s="2" t="inlineStr"/>
+      <c r="T15" s="2" t="inlineStr"/>
+      <c r="U15" s="2" t="inlineStr">
+        <is>
+          <t>07:42</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W15" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X15" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y15" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z15" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr"/>
+      <c r="AC15" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr"/>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr"/>
+      <c r="K16" s="2" t="inlineStr"/>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr"/>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr"/>
+      <c r="R16" s="2" t="inlineStr"/>
+      <c r="S16" s="2" t="inlineStr"/>
+      <c r="T16" s="2" t="inlineStr"/>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>07:45</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X16" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y16" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AC16" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr"/>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr"/>
+      <c r="K17" s="2" t="inlineStr"/>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr"/>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr"/>
+      <c r="R17" s="2" t="inlineStr"/>
+      <c r="S17" s="2" t="inlineStr"/>
+      <c r="T17" s="2" t="inlineStr"/>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>07:57</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X17" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y17" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr"/>
+      <c r="AC17" s="2" t="inlineStr">
+        <is>
+          <t>—/15</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC17"/>
+  <dimension ref="A1:AC27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -441,7 +441,7 @@
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
     <col width="26" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="12" max="12"/>
     <col width="22" customWidth="1" min="13" max="13"/>
     <col width="14" customWidth="1" min="14" max="14"/>
     <col width="14" customWidth="1" min="15" max="15"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -715,7 +715,7 @@
       <c r="AB2" s="2" t="inlineStr"/>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -743,32 +743,36 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:05</t>
         </is>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>100分钟</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr"/>
       <c r="K3" s="2" t="inlineStr"/>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M3" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N3" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -776,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -800,33 +804,37 @@
       </c>
       <c r="W3" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X3" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y3" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB3" s="2" t="inlineStr"/>
+      <c r="AB3" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -887,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -926,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -937,7 +945,7 @@
       <c r="AB4" s="2" t="inlineStr"/>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -965,32 +973,36 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:12</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr"/>
       <c r="K5" s="2" t="inlineStr"/>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -998,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1022,33 +1034,37 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X5" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y5" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB5" s="2" t="inlineStr"/>
+      <c r="AB5" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1109,7 +1125,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1148,7 +1164,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1159,7 +1175,7 @@
       <c r="AB6" s="2" t="inlineStr"/>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1187,32 +1203,36 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:18</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr"/>
       <c r="K7" s="2" t="inlineStr"/>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1220,7 +1240,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1244,33 +1264,37 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X7" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y7" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" s="2" t="inlineStr"/>
+      <c r="AB7" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1298,32 +1322,36 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -1331,7 +1359,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1355,33 +1383,37 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X8" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y8" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB8" s="2" t="inlineStr"/>
+      <c r="AB8" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1442,7 +1474,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1492,7 +1524,7 @@
       <c r="AB9" s="2" t="inlineStr"/>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1553,7 +1585,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1603,7 +1635,7 @@
       <c r="AB10" s="2" t="inlineStr"/>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1696,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1703,7 +1735,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1714,7 +1746,7 @@
       <c r="AB11" s="2" t="inlineStr"/>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1775,7 +1807,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1825,7 +1857,7 @@
       <c r="AB12" s="2" t="inlineStr"/>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1886,7 +1918,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1936,7 +1968,7 @@
       <c r="AB13" s="2" t="inlineStr"/>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2029,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2047,7 +2079,7 @@
       <c r="AB14" s="2" t="inlineStr"/>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2108,7 +2140,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2158,7 +2190,7 @@
       <c r="AB15" s="2" t="inlineStr"/>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2219,7 +2251,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2269,7 +2301,7 @@
       <c r="AB16" s="2" t="inlineStr"/>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
         </is>
       </c>
     </row>
@@ -2277,22 +2309,22 @@
       <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>沪A35616D</t>
+          <t>沪A52736D</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>07:54</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>07:57</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2325,12 +2357,12 @@
       <c r="M17" s="2" t="inlineStr"/>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>08:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2344,7 +2376,7 @@
       <c r="T17" s="2" t="inlineStr"/>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>07:57</t>
+          <t>07:54</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2369,7 +2401,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2380,7 +2412,1133 @@
       <c r="AB17" s="2" t="inlineStr"/>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/15</t>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr"/>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr"/>
+      <c r="K18" s="2" t="inlineStr"/>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr"/>
+      <c r="R18" s="2" t="inlineStr"/>
+      <c r="S18" s="2" t="inlineStr"/>
+      <c r="T18" s="2" t="inlineStr"/>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>08:02</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X18" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y18" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr"/>
+      <c r="AC18" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr"/>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr"/>
+      <c r="K19" s="2" t="inlineStr"/>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr"/>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr"/>
+      <c r="R19" s="2" t="inlineStr"/>
+      <c r="S19" s="2" t="inlineStr"/>
+      <c r="T19" s="2" t="inlineStr"/>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>08:06</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X19" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y19" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA19" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr"/>
+      <c r="AC19" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr"/>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr"/>
+      <c r="K20" s="2" t="inlineStr"/>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr"/>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q20" s="2" t="inlineStr"/>
+      <c r="R20" s="2" t="inlineStr"/>
+      <c r="S20" s="2" t="inlineStr"/>
+      <c r="T20" s="2" t="inlineStr"/>
+      <c r="U20" s="2" t="inlineStr">
+        <is>
+          <t>08:09</t>
+        </is>
+      </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W20" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X20" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y20" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z20" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB20" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC20" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr"/>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O21" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P21" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q21" s="2" t="inlineStr"/>
+      <c r="R21" s="2" t="inlineStr"/>
+      <c r="S21" s="2" t="inlineStr"/>
+      <c r="T21" s="2" t="inlineStr"/>
+      <c r="U21" s="2" t="inlineStr">
+        <is>
+          <t>08:18</t>
+        </is>
+      </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W21" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X21" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y21" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z21" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB21" s="2" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="AC21" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr"/>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>沪A36930D</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr"/>
+      <c r="K22" s="2" t="inlineStr"/>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr"/>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>07:30</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr"/>
+      <c r="R22" s="2" t="inlineStr"/>
+      <c r="S22" s="2" t="inlineStr"/>
+      <c r="T22" s="2" t="inlineStr"/>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>08:21</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X22" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y22" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA22" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr"/>
+      <c r="AC22" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr"/>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr"/>
+      <c r="K23" s="2" t="inlineStr"/>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr"/>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr"/>
+      <c r="R23" s="2" t="inlineStr"/>
+      <c r="S23" s="2" t="inlineStr"/>
+      <c r="T23" s="2" t="inlineStr"/>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>08:30</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X23" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y23" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB23" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC23" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr"/>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr"/>
+      <c r="K24" s="2" t="inlineStr"/>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr"/>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr"/>
+      <c r="R24" s="2" t="inlineStr"/>
+      <c r="S24" s="2" t="inlineStr"/>
+      <c r="T24" s="2" t="inlineStr"/>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>08:33</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X24" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y24" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr"/>
+      <c r="AC24" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr"/>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr"/>
+      <c r="K25" s="2" t="inlineStr"/>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr"/>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr"/>
+      <c r="R25" s="2" t="inlineStr"/>
+      <c r="S25" s="2" t="inlineStr"/>
+      <c r="T25" s="2" t="inlineStr"/>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W25" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X25" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y25" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z25" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB25" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC25" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr"/>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr"/>
+      <c r="K26" s="2" t="inlineStr"/>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q26" s="2" t="inlineStr"/>
+      <c r="R26" s="2" t="inlineStr"/>
+      <c r="S26" s="2" t="inlineStr"/>
+      <c r="T26" s="2" t="inlineStr"/>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>08:45</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X26" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y26" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z26" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA26" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr"/>
+      <c r="AC26" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr"/>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr"/>
+      <c r="K27" s="2" t="inlineStr"/>
+      <c r="L27" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr"/>
+      <c r="N27" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O27" s="2" t="inlineStr">
+        <is>
+          <t>08:20</t>
+        </is>
+      </c>
+      <c r="P27" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q27" s="2" t="inlineStr"/>
+      <c r="R27" s="2" t="inlineStr"/>
+      <c r="S27" s="2" t="inlineStr"/>
+      <c r="T27" s="2" t="inlineStr"/>
+      <c r="U27" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W27" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X27" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y27" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z27" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA27" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr"/>
+      <c r="AC27" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC27"/>
+  <dimension ref="A1:AC33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1092,32 +1092,36 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr"/>
       <c r="K6" s="2" t="inlineStr"/>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -1125,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1149,17 +1153,17 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X6" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y6" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z6" s="2" t="inlineStr">
@@ -1169,13 +1173,17 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB6" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB6" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1240,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1294,7 +1302,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1332,24 +1340,24 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:31</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>90分钟</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr"/>
       <c r="K8" s="2" t="inlineStr"/>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1359,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1408,12 +1416,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1474,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1513,7 +1521,7 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
@@ -1552,32 +1560,36 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:03</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>113分钟</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr"/>
       <c r="K10" s="2" t="inlineStr"/>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1585,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1609,33 +1621,37 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X10" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y10" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB10" s="2" t="inlineStr"/>
+      <c r="AB10" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1663,32 +1679,36 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>08:42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr"/>
       <c r="K11" s="2" t="inlineStr"/>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -1696,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1720,17 +1740,17 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X11" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y11" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z11" s="2" t="inlineStr">
@@ -1740,13 +1760,17 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB11" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB11" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1774,32 +1798,36 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>110分钟</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr"/>
       <c r="K12" s="2" t="inlineStr"/>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1807,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1831,33 +1859,37 @@
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X12" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y12" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB12" s="2" t="inlineStr"/>
+      <c r="AB12" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1885,32 +1917,36 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:08</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr"/>
       <c r="K13" s="2" t="inlineStr"/>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -1918,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -1942,33 +1978,37 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X13" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y13" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB13" s="2" t="inlineStr"/>
+      <c r="AB13" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2029,7 +2069,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2068,7 +2108,7 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA14" s="2" t="inlineStr">
@@ -2140,7 +2180,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2218,32 +2258,36 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:24</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>99分钟</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr"/>
       <c r="K16" s="2" t="inlineStr"/>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2251,7 +2295,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2275,33 +2319,37 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X16" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y16" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB16" s="2" t="inlineStr"/>
+      <c r="AB16" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2362,7 +2410,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2473,7 +2521,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2584,7 +2632,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2695,7 +2743,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2749,7 +2797,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2810,7 +2858,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2864,7 +2912,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2925,7 +2973,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3036,7 +3084,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3090,7 +3138,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3151,7 +3199,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3262,7 +3310,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3311,12 +3359,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3377,7 +3425,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3421,13 +3469,17 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB26" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB26" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3435,22 +3487,22 @@
       <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>沪A59117D</t>
+          <t>沪A35591D</t>
         </is>
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>08:57</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>09:00</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -3483,12 +3535,12 @@
       <c r="M27" s="2" t="inlineStr"/>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>06:50</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>08:20</t>
+          <t>09:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3502,7 +3554,7 @@
       <c r="T27" s="2" t="inlineStr"/>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:57</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
@@ -3539,6 +3591,692 @@
       <c r="AC27" s="2" t="inlineStr">
         <is>
           <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr"/>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr"/>
+      <c r="K28" s="2" t="inlineStr"/>
+      <c r="L28" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr"/>
+      <c r="N28" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O28" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P28" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q28" s="2" t="inlineStr"/>
+      <c r="R28" s="2" t="inlineStr"/>
+      <c r="S28" s="2" t="inlineStr"/>
+      <c r="T28" s="2" t="inlineStr"/>
+      <c r="U28" s="2" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W28" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X28" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y28" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z28" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB28" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC28" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr"/>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O29" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P29" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q29" s="2" t="inlineStr"/>
+      <c r="R29" s="2" t="inlineStr"/>
+      <c r="S29" s="2" t="inlineStr"/>
+      <c r="T29" s="2" t="inlineStr"/>
+      <c r="U29" s="2" t="inlineStr">
+        <is>
+          <t>09:10</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W29" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X29" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y29" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z29" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA29" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB29" s="2" t="inlineStr">
+        <is>
+          <t>113.0</t>
+        </is>
+      </c>
+      <c r="AC29" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr"/>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr"/>
+      <c r="K30" s="2" t="inlineStr"/>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr"/>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr"/>
+      <c r="R30" s="2" t="inlineStr"/>
+      <c r="S30" s="2" t="inlineStr"/>
+      <c r="T30" s="2" t="inlineStr"/>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>09:15</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W30" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X30" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y30" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB30" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
+      <c r="AC30" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr"/>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr"/>
+      <c r="K31" s="2" t="inlineStr"/>
+      <c r="L31" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr"/>
+      <c r="N31" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O31" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P31" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q31" s="2" t="inlineStr"/>
+      <c r="R31" s="2" t="inlineStr"/>
+      <c r="S31" s="2" t="inlineStr"/>
+      <c r="T31" s="2" t="inlineStr"/>
+      <c r="U31" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W31" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X31" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y31" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB31" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC31" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr"/>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr"/>
+      <c r="K32" s="2" t="inlineStr"/>
+      <c r="L32" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr"/>
+      <c r="N32" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O32" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P32" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr"/>
+      <c r="R32" s="2" t="inlineStr"/>
+      <c r="S32" s="2" t="inlineStr"/>
+      <c r="T32" s="2" t="inlineStr"/>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X32" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y32" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z32" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr"/>
+      <c r="AC32" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr"/>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr"/>
+      <c r="K33" s="2" t="inlineStr"/>
+      <c r="L33" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr"/>
+      <c r="N33" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O33" s="2" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="P33" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q33" s="2" t="inlineStr"/>
+      <c r="R33" s="2" t="inlineStr"/>
+      <c r="S33" s="2" t="inlineStr"/>
+      <c r="T33" s="2" t="inlineStr"/>
+      <c r="U33" s="2" t="inlineStr">
+        <is>
+          <t>09:30</t>
+        </is>
+      </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W33" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X33" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y33" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z33" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB33" s="2" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="AC33" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC33"/>
+  <dimension ref="A1:AC36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -819,7 +819,7 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA3" s="2" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +895,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -934,7 +934,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -1010,7 +1010,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1183,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1367,7 +1367,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1482,7 +1482,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1716,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1954,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2036,32 +2036,36 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>103分钟</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr"/>
       <c r="K14" s="2" t="inlineStr"/>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -2069,7 +2073,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2093,17 +2097,17 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X14" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y14" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z14" s="2" t="inlineStr">
@@ -2113,13 +2117,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB14" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB14" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2147,32 +2155,36 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:13</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr"/>
       <c r="K15" s="2" t="inlineStr"/>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -2180,7 +2192,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>09:10</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2204,17 +2216,17 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X15" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y15" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z15" s="2" t="inlineStr">
@@ -2224,13 +2236,17 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB15" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB15" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2311,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2349,7 +2365,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2410,7 +2426,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2449,7 +2465,7 @@
       </c>
       <c r="Z17" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA17" s="2" t="inlineStr">
@@ -2521,7 +2537,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2632,7 +2648,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2743,7 +2759,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2782,7 +2798,7 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA20" s="2" t="inlineStr">
@@ -2797,7 +2813,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2858,7 +2874,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2912,7 +2928,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2973,7 +2989,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3084,7 +3100,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3199,7 +3215,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3238,7 +3254,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3310,7 +3326,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,7 +3441,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3479,7 +3495,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3556,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3651,7 +3667,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3766,7 +3782,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3820,7 +3836,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3881,7 +3897,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3935,7 +3951,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3996,7 +4012,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4050,7 +4066,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4127,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4155,13 +4171,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB32" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB32" s="2" t="inlineStr">
+        <is>
+          <t>103.0</t>
+        </is>
+      </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4222,7 +4242,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:01</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4276,7 +4296,344 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr"/>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>沪A52736D</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr"/>
+      <c r="K34" s="2" t="inlineStr"/>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr"/>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P34" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q34" s="2" t="inlineStr"/>
+      <c r="R34" s="2" t="inlineStr"/>
+      <c r="S34" s="2" t="inlineStr"/>
+      <c r="T34" s="2" t="inlineStr"/>
+      <c r="U34" s="2" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W34" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X34" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y34" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z34" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA34" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr"/>
+      <c r="AC34" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr"/>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr"/>
+      <c r="K35" s="2" t="inlineStr"/>
+      <c r="L35" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr"/>
+      <c r="N35" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O35" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P35" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q35" s="2" t="inlineStr"/>
+      <c r="R35" s="2" t="inlineStr"/>
+      <c r="S35" s="2" t="inlineStr"/>
+      <c r="T35" s="2" t="inlineStr"/>
+      <c r="U35" s="2" t="inlineStr">
+        <is>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W35" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X35" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y35" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB35" s="2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AC35" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr"/>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr"/>
+      <c r="K36" s="2" t="inlineStr"/>
+      <c r="L36" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr"/>
+      <c r="N36" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O36" s="2" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="P36" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q36" s="2" t="inlineStr"/>
+      <c r="R36" s="2" t="inlineStr"/>
+      <c r="S36" s="2" t="inlineStr"/>
+      <c r="T36" s="2" t="inlineStr"/>
+      <c r="U36" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr"/>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>—/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC36"/>
+  <dimension ref="A1:AC42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,13 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB2" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB2" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -780,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -824,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -895,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -939,13 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB4" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1010,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1049,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1183,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1287,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1367,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1406,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1482,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1521,18 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB9" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB9" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1641,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1716,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1755,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA11" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1835,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1874,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1889,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1954,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2008,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2073,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2127,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2246,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2311,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2365,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2426,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2504,32 +2516,36 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:35</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>93分钟</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr"/>
       <c r="K18" s="2" t="inlineStr"/>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2537,7 +2553,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2561,17 +2577,17 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X18" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y18" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z18" s="2" t="inlineStr">
@@ -2581,13 +2597,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB18" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB18" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2615,32 +2635,36 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:34</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr"/>
       <c r="K19" s="2" t="inlineStr"/>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -2648,7 +2672,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2672,17 +2696,17 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X19" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y19" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z19" s="2" t="inlineStr">
@@ -2692,13 +2716,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB19" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB19" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2726,32 +2754,36 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:44</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr"/>
       <c r="K20" s="2" t="inlineStr"/>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -2759,7 +2791,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2783,17 +2815,17 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X20" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y20" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z20" s="2" t="inlineStr">
@@ -2803,17 +2835,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2841,32 +2873,36 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:48</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr"/>
       <c r="K21" s="2" t="inlineStr"/>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -2874,7 +2910,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2898,37 +2934,37 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X21" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y21" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2956,32 +2992,36 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:59</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr"/>
       <c r="K22" s="2" t="inlineStr"/>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M22" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
           <t>07:30</t>
@@ -2989,7 +3029,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:50</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -3013,17 +3053,17 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X22" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y22" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z22" s="2" t="inlineStr">
@@ -3033,13 +3073,17 @@
       </c>
       <c r="AA22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB22" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB22" s="2" t="inlineStr">
+        <is>
+          <t>98.0</t>
+        </is>
+      </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3067,32 +3111,36 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr"/>
       <c r="K23" s="2" t="inlineStr"/>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3100,7 +3148,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3124,37 +3172,37 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X23" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y23" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA23" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3182,32 +3230,36 @@
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr"/>
       <c r="K24" s="2" t="inlineStr"/>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -3215,7 +3267,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3239,17 +3291,17 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X24" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y24" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z24" s="2" t="inlineStr">
@@ -3259,13 +3311,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB24" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB24" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3293,32 +3349,36 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr"/>
       <c r="K25" s="2" t="inlineStr"/>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3326,7 +3386,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3350,37 +3410,37 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X25" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y25" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3441,7 +3501,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3495,7 +3555,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3523,32 +3583,36 @@
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr"/>
       <c r="K27" s="2" t="inlineStr"/>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M27" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M27" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -3556,7 +3620,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3580,33 +3644,37 @@
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X27" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y27" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB27" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB27" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3634,32 +3702,36 @@
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr"/>
       <c r="K28" s="2" t="inlineStr"/>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M28" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M28" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3667,7 +3739,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3691,37 +3763,37 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X28" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y28" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA28" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA28" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3749,32 +3821,36 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr"/>
       <c r="K29" s="2" t="inlineStr"/>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M29" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M29" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -3782,7 +3858,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3806,17 +3882,17 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X29" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y29" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z29" s="2" t="inlineStr">
@@ -3826,17 +3902,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>113.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3897,7 +3973,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3951,7 +4027,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4088,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4051,7 +4127,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4066,7 +4142,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4127,7 +4203,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4181,7 +4257,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4242,7 +4318,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4296,7 +4372,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4357,7 +4433,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4468,7 +4544,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4512,17 +4588,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4530,22 +4606,22 @@
       <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>沪A36809D</t>
+          <t>沪A61166D</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>10:20</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -4578,12 +4654,12 @@
       <c r="M36" s="2" t="inlineStr"/>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>06:01</t>
+          <t>06:30</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>10:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4597,43 +4673,737 @@
       <c r="T36" s="2" t="inlineStr"/>
       <c r="U36" s="2" t="inlineStr">
         <is>
+          <t>10:10</t>
+        </is>
+      </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W36" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X36" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y36" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB36" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC36" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr"/>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>10:20</t>
         </is>
       </c>
-      <c r="V36" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P37" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q37" s="2" t="inlineStr"/>
+      <c r="R37" s="2" t="inlineStr"/>
+      <c r="S37" s="2" t="inlineStr"/>
+      <c r="T37" s="2" t="inlineStr"/>
+      <c r="U37" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V37" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W36" s="2" t="inlineStr">
+      <c r="W37" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X36" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y36" s="2" t="inlineStr">
+      <c r="X37" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y37" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z36" s="2" t="inlineStr">
+      <c r="Z37" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB36" s="2" t="inlineStr"/>
-      <c r="AC36" s="2" t="inlineStr">
-        <is>
-          <t>—/18</t>
+      <c r="AA37" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB37" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC37" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr"/>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr"/>
+      <c r="K38" s="2" t="inlineStr"/>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr"/>
+      <c r="N38" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P38" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q38" s="2" t="inlineStr"/>
+      <c r="R38" s="2" t="inlineStr"/>
+      <c r="S38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr"/>
+      <c r="U38" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W38" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X38" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y38" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z38" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA38" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB38" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC38" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr"/>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O39" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P39" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q39" s="2" t="inlineStr"/>
+      <c r="R39" s="2" t="inlineStr"/>
+      <c r="S39" s="2" t="inlineStr"/>
+      <c r="T39" s="2" t="inlineStr"/>
+      <c r="U39" s="2" t="inlineStr">
+        <is>
+          <t>10:35</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W39" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X39" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y39" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB39" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC39" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr"/>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O40" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P40" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr"/>
+      <c r="R40" s="2" t="inlineStr"/>
+      <c r="S40" s="2" t="inlineStr"/>
+      <c r="T40" s="2" t="inlineStr"/>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X40" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y40" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z40" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA40" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB40" s="2" t="inlineStr">
+        <is>
+          <t>76.0</t>
+        </is>
+      </c>
+      <c r="AC40" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr"/>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O41" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P41" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q41" s="2" t="inlineStr"/>
+      <c r="R41" s="2" t="inlineStr"/>
+      <c r="S41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr"/>
+      <c r="U41" s="2" t="inlineStr">
+        <is>
+          <t>10:45</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W41" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X41" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y41" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z41" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA41" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB41" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC41" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr"/>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O42" s="2" t="inlineStr">
+        <is>
+          <t>10:20</t>
+        </is>
+      </c>
+      <c r="P42" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q42" s="2" t="inlineStr"/>
+      <c r="R42" s="2" t="inlineStr"/>
+      <c r="S42" s="2" t="inlineStr"/>
+      <c r="T42" s="2" t="inlineStr"/>
+      <c r="U42" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>110.0</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC42"/>
+  <dimension ref="A1:AC49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,12 +938,12 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1191,7 +1191,7 @@
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -2482,13 +2482,17 @@
       </c>
       <c r="AA17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB17" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB17" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2607,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2726,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2830,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2910,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2949,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3202,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3267,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3306,12 +3310,12 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
@@ -3321,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3425,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3555,7 +3559,7 @@
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3620,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3739,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3858,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3912,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3940,32 +3944,36 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr"/>
       <c r="K30" s="2" t="inlineStr"/>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M30" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -3973,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -3997,37 +4005,37 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X30" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y30" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>98.0</t>
+          <t>90.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4055,32 +4063,36 @@
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:43</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr"/>
       <c r="K31" s="2" t="inlineStr"/>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M31" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -4088,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4112,17 +4124,17 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X31" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y31" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z31" s="2" t="inlineStr">
@@ -4132,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>110.0</t>
+          <t>96.5</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4170,32 +4182,36 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr"/>
       <c r="K32" s="2" t="inlineStr"/>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M32" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M32" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -4203,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4227,37 +4243,37 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X32" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y32" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>91.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4285,32 +4301,36 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr"/>
       <c r="K33" s="2" t="inlineStr"/>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M33" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M33" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4318,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4342,37 +4362,37 @@
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X33" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y33" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4400,32 +4420,36 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr"/>
       <c r="K34" s="2" t="inlineStr"/>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4433,7 +4457,7 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
@@ -4457,17 +4481,17 @@
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X34" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y34" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z34" s="2" t="inlineStr">
@@ -4477,13 +4501,17 @@
       </c>
       <c r="AA34" s="2" t="inlineStr">
         <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB34" s="2" t="inlineStr"/>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB34" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>—/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4511,32 +4539,36 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr"/>
       <c r="K35" s="2" t="inlineStr"/>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M35" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M35" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4544,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4568,37 +4600,37 @@
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X35" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y35" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4626,32 +4658,36 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:32</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M36" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M36" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -4659,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4683,37 +4719,37 @@
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X36" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y36" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4741,32 +4777,36 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr"/>
       <c r="K37" s="2" t="inlineStr"/>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M37" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M37" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -4774,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4798,27 +4838,27 @@
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X37" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y37" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
@@ -4828,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4889,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>10:50</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4943,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4971,32 +5011,36 @@
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M39" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M39" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5004,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5028,37 +5072,37 @@
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X39" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y39" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.3</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5163,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5234,7 +5278,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5296,22 +5340,22 @@
       <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>沪A56123D</t>
+          <t>沪A35186D</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>11:10</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -5349,7 +5393,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>10:20</t>
+          <t>11:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5363,47 +5407,852 @@
       <c r="T42" s="2" t="inlineStr"/>
       <c r="U42" s="2" t="inlineStr">
         <is>
+          <t>11:00</t>
+        </is>
+      </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W42" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X42" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y42" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z42" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB42" s="2" t="inlineStr">
+        <is>
+          <t>90.5</t>
+        </is>
+      </c>
+      <c r="AC42" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr"/>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
           <t>11:10</t>
         </is>
       </c>
-      <c r="V42" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J43" s="2" t="inlineStr"/>
+      <c r="K43" s="2" t="inlineStr"/>
+      <c r="L43" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr"/>
+      <c r="N43" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O43" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P43" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q43" s="2" t="inlineStr"/>
+      <c r="R43" s="2" t="inlineStr"/>
+      <c r="S43" s="2" t="inlineStr"/>
+      <c r="T43" s="2" t="inlineStr"/>
+      <c r="U43" s="2" t="inlineStr">
+        <is>
+          <t>11:10</t>
+        </is>
+      </c>
+      <c r="V43" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W42" s="2" t="inlineStr">
+      <c r="W43" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X42" s="2" t="inlineStr">
-        <is>
-          <t>待确认</t>
-        </is>
-      </c>
-      <c r="Y42" s="2" t="inlineStr">
+      <c r="X43" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y43" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z42" s="2" t="inlineStr">
+      <c r="Z43" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AB42" s="2" t="inlineStr">
-        <is>
-          <t>110.0</t>
-        </is>
-      </c>
-      <c r="AC42" s="2" t="inlineStr">
-        <is>
-          <t>16/18</t>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB43" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC43" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr"/>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J44" s="2" t="inlineStr"/>
+      <c r="K44" s="2" t="inlineStr"/>
+      <c r="L44" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr"/>
+      <c r="N44" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O44" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P44" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q44" s="2" t="inlineStr"/>
+      <c r="R44" s="2" t="inlineStr"/>
+      <c r="S44" s="2" t="inlineStr"/>
+      <c r="T44" s="2" t="inlineStr"/>
+      <c r="U44" s="2" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W44" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X44" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y44" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB44" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC44" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr"/>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J45" s="2" t="inlineStr"/>
+      <c r="K45" s="2" t="inlineStr"/>
+      <c r="L45" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr"/>
+      <c r="N45" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O45" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P45" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q45" s="2" t="inlineStr"/>
+      <c r="R45" s="2" t="inlineStr"/>
+      <c r="S45" s="2" t="inlineStr"/>
+      <c r="T45" s="2" t="inlineStr"/>
+      <c r="U45" s="2" t="inlineStr">
+        <is>
+          <t>11:35</t>
+        </is>
+      </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W45" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X45" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y45" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB45" s="2" t="inlineStr">
+        <is>
+          <t>91.5</t>
+        </is>
+      </c>
+      <c r="AC45" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr"/>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J46" s="2" t="inlineStr"/>
+      <c r="K46" s="2" t="inlineStr"/>
+      <c r="L46" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr"/>
+      <c r="N46" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O46" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P46" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q46" s="2" t="inlineStr"/>
+      <c r="R46" s="2" t="inlineStr"/>
+      <c r="S46" s="2" t="inlineStr"/>
+      <c r="T46" s="2" t="inlineStr"/>
+      <c r="U46" s="2" t="inlineStr">
+        <is>
+          <t>11:50</t>
+        </is>
+      </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W46" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X46" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y46" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z46" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB46" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC46" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr"/>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J47" s="2" t="inlineStr"/>
+      <c r="K47" s="2" t="inlineStr"/>
+      <c r="L47" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr"/>
+      <c r="N47" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O47" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P47" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q47" s="2" t="inlineStr"/>
+      <c r="R47" s="2" t="inlineStr"/>
+      <c r="S47" s="2" t="inlineStr"/>
+      <c r="T47" s="2" t="inlineStr"/>
+      <c r="U47" s="2" t="inlineStr">
+        <is>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W47" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X47" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y47" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z47" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB47" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC47" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr"/>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O48" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P48" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q48" s="2" t="inlineStr"/>
+      <c r="R48" s="2" t="inlineStr"/>
+      <c r="S48" s="2" t="inlineStr"/>
+      <c r="T48" s="2" t="inlineStr"/>
+      <c r="U48" s="2" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W48" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X48" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y48" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z48" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA48" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB48" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC48" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr"/>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J49" s="2" t="inlineStr"/>
+      <c r="K49" s="2" t="inlineStr"/>
+      <c r="L49" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr"/>
+      <c r="N49" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O49" s="2" t="inlineStr">
+        <is>
+          <t>11:20</t>
+        </is>
+      </c>
+      <c r="P49" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q49" s="2" t="inlineStr"/>
+      <c r="R49" s="2" t="inlineStr"/>
+      <c r="S49" s="2" t="inlineStr"/>
+      <c r="T49" s="2" t="inlineStr"/>
+      <c r="U49" s="2" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W49" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X49" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y49" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z49" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB49" s="2" t="inlineStr">
+        <is>
+          <t>86.3</t>
+        </is>
+      </c>
+      <c r="AC49" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC49"/>
+  <dimension ref="A1:AC54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1067,12 +1067,12 @@
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,22 +2362,22 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2963,12 +2963,12 @@
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,17 +4258,17 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,22 +4377,22 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4668,24 +4668,24 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>11:32</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr"/>
       <c r="K36" s="2" t="inlineStr"/>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4744,12 +4744,12 @@
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5021,24 +5021,24 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr"/>
       <c r="K39" s="2" t="inlineStr"/>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5130,32 +5130,36 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:10</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr"/>
       <c r="K40" s="2" t="inlineStr"/>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M40" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M40" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5163,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5187,32 +5191,32 @@
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X40" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y40" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>76.0</t>
+          <t>80.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5360,32 +5364,36 @@
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:21</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr"/>
       <c r="K42" s="2" t="inlineStr"/>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M42" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M42" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5393,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5417,37 +5425,37 @@
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X42" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y42" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>90.5</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5475,32 +5483,36 @@
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="I43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J43" s="2" t="inlineStr"/>
       <c r="K43" s="2" t="inlineStr"/>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M43" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M43" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N43" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -5508,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5532,37 +5544,37 @@
       </c>
       <c r="W43" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X43" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y43" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>92.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5590,32 +5602,36 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>12:45</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M44" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M44" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N44" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5623,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5647,37 +5663,37 @@
       </c>
       <c r="W44" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X44" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y44" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5705,32 +5721,36 @@
       </c>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
       <c r="K45" s="2" t="inlineStr"/>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M45" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M45" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N45" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -5738,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5762,32 +5782,32 @@
       </c>
       <c r="W45" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X45" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y45" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>91.5</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5853,7 +5873,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5907,7 +5927,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5968,7 +5988,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6017,12 +6037,12 @@
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6083,7 +6103,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6137,7 +6157,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6198,7 +6218,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6247,12 +6267,587 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.3</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr"/>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="inlineStr"/>
+      <c r="K50" s="2" t="inlineStr"/>
+      <c r="L50" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr"/>
+      <c r="N50" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O50" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P50" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q50" s="2" t="inlineStr"/>
+      <c r="R50" s="2" t="inlineStr"/>
+      <c r="S50" s="2" t="inlineStr"/>
+      <c r="T50" s="2" t="inlineStr"/>
+      <c r="U50" s="2" t="inlineStr">
+        <is>
+          <t>12:40</t>
+        </is>
+      </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W50" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X50" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y50" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z50" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA50" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB50" s="2" t="inlineStr">
+        <is>
+          <t>80.5</t>
+        </is>
+      </c>
+      <c r="AC50" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr"/>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J51" s="2" t="inlineStr"/>
+      <c r="K51" s="2" t="inlineStr"/>
+      <c r="L51" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr"/>
+      <c r="N51" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O51" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P51" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q51" s="2" t="inlineStr"/>
+      <c r="R51" s="2" t="inlineStr"/>
+      <c r="S51" s="2" t="inlineStr"/>
+      <c r="T51" s="2" t="inlineStr"/>
+      <c r="U51" s="2" t="inlineStr">
+        <is>
+          <t>12:50</t>
+        </is>
+      </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W51" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X51" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y51" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z51" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB51" s="2" t="inlineStr">
+        <is>
+          <t>87.3</t>
+        </is>
+      </c>
+      <c r="AC51" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr"/>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J52" s="2" t="inlineStr"/>
+      <c r="K52" s="2" t="inlineStr"/>
+      <c r="L52" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr"/>
+      <c r="N52" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O52" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P52" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q52" s="2" t="inlineStr"/>
+      <c r="R52" s="2" t="inlineStr"/>
+      <c r="S52" s="2" t="inlineStr"/>
+      <c r="T52" s="2" t="inlineStr"/>
+      <c r="U52" s="2" t="inlineStr">
+        <is>
+          <t>13:05</t>
+        </is>
+      </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W52" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X52" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y52" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z52" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB52" s="2" t="inlineStr">
+        <is>
+          <t>92.7</t>
+        </is>
+      </c>
+      <c r="AC52" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr"/>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J53" s="2" t="inlineStr"/>
+      <c r="K53" s="2" t="inlineStr"/>
+      <c r="L53" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr"/>
+      <c r="N53" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O53" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P53" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q53" s="2" t="inlineStr"/>
+      <c r="R53" s="2" t="inlineStr"/>
+      <c r="S53" s="2" t="inlineStr"/>
+      <c r="T53" s="2" t="inlineStr"/>
+      <c r="U53" s="2" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W53" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X53" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y53" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z53" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB53" s="2" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="AC53" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr"/>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J54" s="2" t="inlineStr"/>
+      <c r="K54" s="2" t="inlineStr"/>
+      <c r="L54" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr"/>
+      <c r="N54" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O54" s="2" t="inlineStr">
+        <is>
+          <t>12:20</t>
+        </is>
+      </c>
+      <c r="P54" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q54" s="2" t="inlineStr"/>
+      <c r="R54" s="2" t="inlineStr"/>
+      <c r="S54" s="2" t="inlineStr"/>
+      <c r="T54" s="2" t="inlineStr"/>
+      <c r="U54" s="2" t="inlineStr">
+        <is>
+          <t>13:30</t>
+        </is>
+      </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W54" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X54" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y54" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z54" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB54" s="2" t="inlineStr">
+        <is>
+          <t>90.0</t>
+        </is>
+      </c>
+      <c r="AC54" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC54"/>
+  <dimension ref="A1:AC59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>09:40</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4268,7 +4268,7 @@
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,12 +4387,12 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5455,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5574,7 +5574,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5612,24 +5612,24 @@
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>12:45</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="I44" s="2" t="inlineStr">
         <is>
-          <t>80分钟</t>
+          <t>76分钟</t>
         </is>
       </c>
       <c r="J44" s="2" t="inlineStr"/>
       <c r="K44" s="2" t="inlineStr"/>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N44" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5731,12 +5731,12 @@
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J45" s="2" t="inlineStr"/>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5807,7 +5807,7 @@
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
@@ -5840,32 +5840,36 @@
       </c>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:10</t>
         </is>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J46" s="2" t="inlineStr"/>
       <c r="K46" s="2" t="inlineStr"/>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M46" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M46" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N46" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -5873,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5897,37 +5901,37 @@
       </c>
       <c r="W46" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X46" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y46" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5955,32 +5959,36 @@
       </c>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J47" s="2" t="inlineStr"/>
       <c r="K47" s="2" t="inlineStr"/>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M47" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M47" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N47" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -5988,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6012,37 +6020,37 @@
       </c>
       <c r="W47" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X47" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y47" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6070,32 +6078,36 @@
       </c>
       <c r="F48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:40</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M48" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M48" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N48" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6103,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6127,37 +6139,37 @@
       </c>
       <c r="W48" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X48" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y48" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6185,32 +6197,36 @@
       </c>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>13:49</t>
         </is>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J49" s="2" t="inlineStr"/>
       <c r="K49" s="2" t="inlineStr"/>
       <c r="L49" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M49" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M49" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N49" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6218,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6242,37 +6258,37 @@
       </c>
       <c r="W49" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X49" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y49" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.0</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6349,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6448,7 +6464,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6502,7 +6518,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6563,7 +6579,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6617,7 +6633,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6678,7 +6694,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6727,12 +6743,12 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>87.3</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6793,7 +6809,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6842,12 +6858,587 @@
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
           <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr"/>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J55" s="2" t="inlineStr"/>
+      <c r="K55" s="2" t="inlineStr"/>
+      <c r="L55" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr"/>
+      <c r="N55" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O55" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P55" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q55" s="2" t="inlineStr"/>
+      <c r="R55" s="2" t="inlineStr"/>
+      <c r="S55" s="2" t="inlineStr"/>
+      <c r="T55" s="2" t="inlineStr"/>
+      <c r="U55" s="2" t="inlineStr">
+        <is>
+          <t>13:40</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W55" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X55" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y55" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z55" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB55" s="2" t="inlineStr">
+        <is>
+          <t>89.8</t>
+        </is>
+      </c>
+      <c r="AC55" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr"/>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O56" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P56" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q56" s="2" t="inlineStr"/>
+      <c r="R56" s="2" t="inlineStr"/>
+      <c r="S56" s="2" t="inlineStr"/>
+      <c r="T56" s="2" t="inlineStr"/>
+      <c r="U56" s="2" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W56" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X56" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y56" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z56" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB56" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC56" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr"/>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J57" s="2" t="inlineStr"/>
+      <c r="K57" s="2" t="inlineStr"/>
+      <c r="L57" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr"/>
+      <c r="N57" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O57" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P57" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q57" s="2" t="inlineStr"/>
+      <c r="R57" s="2" t="inlineStr"/>
+      <c r="S57" s="2" t="inlineStr"/>
+      <c r="T57" s="2" t="inlineStr"/>
+      <c r="U57" s="2" t="inlineStr">
+        <is>
+          <t>14:00</t>
+        </is>
+      </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W57" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X57" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y57" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z57" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB57" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC57" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr"/>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J58" s="2" t="inlineStr"/>
+      <c r="K58" s="2" t="inlineStr"/>
+      <c r="L58" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr"/>
+      <c r="N58" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O58" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P58" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q58" s="2" t="inlineStr"/>
+      <c r="R58" s="2" t="inlineStr"/>
+      <c r="S58" s="2" t="inlineStr"/>
+      <c r="T58" s="2" t="inlineStr"/>
+      <c r="U58" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W58" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X58" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y58" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z58" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB58" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC58" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr"/>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O59" s="2" t="inlineStr">
+        <is>
+          <t>13:20</t>
+        </is>
+      </c>
+      <c r="P59" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q59" s="2" t="inlineStr"/>
+      <c r="R59" s="2" t="inlineStr"/>
+      <c r="S59" s="2" t="inlineStr"/>
+      <c r="T59" s="2" t="inlineStr"/>
+      <c r="U59" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W59" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X59" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y59" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z59" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA59" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB59" s="2" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="AC59" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC59"/>
+  <dimension ref="A1:AC62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -948,12 +948,12 @@
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,17 +1529,17 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,22 +2005,22 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA13" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>09:10</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,14 +2243,14 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,12 +2367,12 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,17 +3663,17 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,22 +4020,22 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA30" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA30" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,12 +4382,12 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4863,12 +4863,12 @@
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5206,17 +5206,17 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5440,22 +5440,22 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA42" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA42" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5564,17 +5564,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5683,12 +5683,12 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6088,24 +6088,24 @@
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>13:40</t>
+          <t>13:44</t>
         </is>
       </c>
       <c r="I48" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>89分钟</t>
         </is>
       </c>
       <c r="J48" s="2" t="inlineStr"/>
       <c r="K48" s="2" t="inlineStr"/>
       <c r="L48" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N48" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6316,32 +6316,36 @@
       </c>
       <c r="F50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="I50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J50" s="2" t="inlineStr"/>
       <c r="K50" s="2" t="inlineStr"/>
       <c r="L50" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M50" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M50" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N50" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -6349,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6373,32 +6377,32 @@
       </c>
       <c r="W50" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X50" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y50" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>80.5</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
@@ -6431,32 +6435,36 @@
       </c>
       <c r="F51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:14</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M51" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M51" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N51" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6464,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6488,37 +6496,37 @@
       </c>
       <c r="W51" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X51" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y51" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA51" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA51" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6546,32 +6554,36 @@
       </c>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:27</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
       <c r="K52" s="2" t="inlineStr"/>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M52" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M52" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N52" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -6579,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6603,17 +6615,17 @@
       </c>
       <c r="W52" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X52" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y52" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z52" s="2" t="inlineStr">
@@ -6623,17 +6635,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>92.7</t>
+          <t>90.0</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6661,32 +6673,36 @@
       </c>
       <c r="F53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:42</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M53" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M53" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N53" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6694,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6718,17 +6734,17 @@
       </c>
       <c r="W53" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X53" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y53" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z53" s="2" t="inlineStr">
@@ -6738,12 +6754,12 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.3</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6809,7 +6825,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6924,7 +6940,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7039,7 +7055,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7154,7 +7170,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7203,12 +7219,12 @@
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7269,7 +7285,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7384,7 +7400,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>14:01</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7442,6 +7458,351 @@
         </is>
       </c>
     </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr"/>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J60" s="2" t="inlineStr"/>
+      <c r="K60" s="2" t="inlineStr"/>
+      <c r="L60" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr"/>
+      <c r="N60" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O60" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P60" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q60" s="2" t="inlineStr"/>
+      <c r="R60" s="2" t="inlineStr"/>
+      <c r="S60" s="2" t="inlineStr"/>
+      <c r="T60" s="2" t="inlineStr"/>
+      <c r="U60" s="2" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W60" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X60" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y60" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z60" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB60" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC60" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr"/>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O61" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P61" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q61" s="2" t="inlineStr"/>
+      <c r="R61" s="2" t="inlineStr"/>
+      <c r="S61" s="2" t="inlineStr"/>
+      <c r="T61" s="2" t="inlineStr"/>
+      <c r="U61" s="2" t="inlineStr">
+        <is>
+          <t>14:45</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W61" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X61" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y61" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z61" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA61" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB61" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC61" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr"/>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J62" s="2" t="inlineStr"/>
+      <c r="K62" s="2" t="inlineStr"/>
+      <c r="L62" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr"/>
+      <c r="N62" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O62" s="2" t="inlineStr">
+        <is>
+          <t>14:01</t>
+        </is>
+      </c>
+      <c r="P62" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q62" s="2" t="inlineStr"/>
+      <c r="R62" s="2" t="inlineStr"/>
+      <c r="S62" s="2" t="inlineStr"/>
+      <c r="T62" s="2" t="inlineStr"/>
+      <c r="U62" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>14/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC62"/>
+  <dimension ref="A1:AC63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,17 +1886,17 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,17 +4139,17 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4983,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5048,7 +5048,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5167,7 +5167,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5401,7 +5401,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5450,12 +5450,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5559,17 +5559,17 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
@@ -5639,7 +5639,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5688,7 +5688,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5802,17 +5802,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5877,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5996,7 +5996,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6169,7 +6169,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6234,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6353,7 +6353,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6445,24 +6445,24 @@
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>14:14</t>
+          <t>14:13</t>
         </is>
       </c>
       <c r="I51" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J51" s="2" t="inlineStr"/>
       <c r="K51" s="2" t="inlineStr"/>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N51" s="2" t="inlineStr">
@@ -6472,7 +6472,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6521,12 +6521,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6564,12 +6564,12 @@
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>14:27</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>
-          <t>82分钟</t>
+          <t>83分钟</t>
         </is>
       </c>
       <c r="J52" s="2" t="inlineStr"/>
@@ -6591,7 +6591,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6630,17 +6630,17 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.0</t>
+          <t>90.2</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
@@ -6683,24 +6683,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:42</t>
+          <t>14:40</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>87分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6710,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6759,7 +6759,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6792,32 +6792,36 @@
       </c>
       <c r="F54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M54" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M54" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N54" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -6825,7 +6829,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6849,17 +6853,17 @@
       </c>
       <c r="W54" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X54" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y54" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z54" s="2" t="inlineStr">
@@ -6869,17 +6873,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>89.7</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6940,7 +6944,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7055,7 +7059,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7170,7 +7174,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7224,7 +7228,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7285,7 +7289,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7400,7 +7404,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7515,7 +7519,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7630,7 +7634,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7679,12 +7683,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7692,22 +7696,22 @@
       <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A56123D</t>
         </is>
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E62" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -7740,12 +7744,12 @@
       <c r="M62" s="2" t="inlineStr"/>
       <c r="N62" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>07:01</t>
         </is>
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:01</t>
+          <t>14:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7759,45 +7763,160 @@
       <c r="T62" s="2" t="inlineStr"/>
       <c r="U62" s="2" t="inlineStr">
         <is>
+          <t>14:50</t>
+        </is>
+      </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W62" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X62" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y62" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z62" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB62" s="2" t="inlineStr">
+        <is>
+          <t>90.2</t>
+        </is>
+      </c>
+      <c r="AC62" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr"/>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
           <t>15:00</t>
         </is>
       </c>
-      <c r="V62" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J63" s="2" t="inlineStr"/>
+      <c r="K63" s="2" t="inlineStr"/>
+      <c r="L63" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr"/>
+      <c r="N63" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O63" s="2" t="inlineStr">
+        <is>
+          <t>14:20</t>
+        </is>
+      </c>
+      <c r="P63" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q63" s="2" t="inlineStr"/>
+      <c r="R63" s="2" t="inlineStr"/>
+      <c r="S63" s="2" t="inlineStr"/>
+      <c r="T63" s="2" t="inlineStr"/>
+      <c r="U63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V63" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W62" s="2" t="inlineStr">
+      <c r="W63" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X62" s="2" t="inlineStr">
+      <c r="X63" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y62" s="2" t="inlineStr">
+      <c r="Y63" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z62" s="2" t="inlineStr">
+      <c r="Z63" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
+      <c r="AA63" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB62" s="2" t="inlineStr">
+      <c r="AB63" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="AC62" s="2" t="inlineStr">
+      <c r="AC63" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
         </is>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC63"/>
+  <dimension ref="A1:AC73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -436,7 +436,7 @@
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="10" customWidth="1" min="6" max="6"/>
-    <col width="35" customWidth="1" min="7" max="7"/>
+    <col width="36" customWidth="1" min="7" max="7"/>
     <col width="10" customWidth="1" min="8" max="8"/>
     <col width="10" customWidth="1" min="9" max="9"/>
     <col width="18" customWidth="1" min="10" max="10"/>
@@ -449,7 +449,7 @@
     <col width="10" customWidth="1" min="17" max="17"/>
     <col width="16" customWidth="1" min="18" max="18"/>
     <col width="20" customWidth="1" min="19" max="19"/>
-    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="36" customWidth="1" min="20" max="20"/>
     <col width="14" customWidth="1" min="21" max="21"/>
     <col width="14" customWidth="1" min="22" max="22"/>
     <col width="12" customWidth="1" min="23" max="23"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,17 +823,17 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,12 +1057,12 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,7 +1767,7 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,17 +2362,17 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA16" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA16" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,17 +2834,17 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>10:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,17 +4377,17 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA33" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA33" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,17 +4615,17 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,12 +4734,12 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4896,12 @@
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq38，推进13站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>10:50</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4937,10 +4937,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q38" s="2" t="inlineStr"/>
-      <c r="R38" s="2" t="inlineStr"/>
+      <c r="Q38" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R38" s="2" t="inlineStr">
+        <is>
+          <t>10:55</t>
+        </is>
+      </c>
       <c r="S38" s="2" t="inlineStr"/>
-      <c r="T38" s="2" t="inlineStr"/>
+      <c r="T38" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U38" s="2" t="inlineStr">
         <is>
           <t>10:20</t>
@@ -4968,7 +4980,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5048,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5087,12 +5099,12 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
@@ -5167,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5249,12 +5261,12 @@
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>疑似区间车</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq30，推进5站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5282,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>11:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5290,10 +5302,22 @@
           <t>SHMAAS</t>
         </is>
       </c>
-      <c r="Q41" s="2" t="inlineStr"/>
-      <c r="R41" s="2" t="inlineStr"/>
+      <c r="Q41" s="2" t="inlineStr">
+        <is>
+          <t>五莲路凌河路</t>
+        </is>
+      </c>
+      <c r="R41" s="2" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
       <c r="S41" s="2" t="inlineStr"/>
-      <c r="T41" s="2" t="inlineStr"/>
+      <c r="T41" s="2" t="inlineStr">
+        <is>
+          <t>区间折返已由主分类器确认；折返点按重建物理位置seq19映射；现有采样不足以把折返发车时间控制在±10分钟</t>
+        </is>
+      </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>10:45</t>
@@ -5321,7 +5345,7 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
@@ -5401,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5455,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5520,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5639,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5678,17 +5702,17 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA44" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA44" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5758,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5797,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5877,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5916,17 +5940,17 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
@@ -5996,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6035,12 +6059,12 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
@@ -6115,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6159,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6234,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6273,12 +6297,12 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
@@ -6353,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6472,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6526,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6591,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6683,24 +6707,24 @@
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>14:40</t>
+          <t>14:41</t>
         </is>
       </c>
       <c r="I53" s="2" t="inlineStr">
         <is>
-          <t>85分钟</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J53" s="2" t="inlineStr"/>
       <c r="K53" s="2" t="inlineStr"/>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N53" s="2" t="inlineStr">
@@ -6710,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6749,17 +6773,17 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA53" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA53" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6802,24 +6826,24 @@
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:55</t>
         </is>
       </c>
       <c r="I54" s="2" t="inlineStr">
         <is>
-          <t>84分钟</t>
+          <t>85分钟</t>
         </is>
       </c>
       <c r="J54" s="2" t="inlineStr"/>
       <c r="K54" s="2" t="inlineStr"/>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
         </is>
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr">
@@ -6829,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6868,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6911,32 +6935,36 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:04</t>
         </is>
       </c>
       <c r="I55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J55" s="2" t="inlineStr"/>
       <c r="K55" s="2" t="inlineStr"/>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M55" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M55" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N55" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -6944,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -6968,32 +6996,32 @@
       </c>
       <c r="W55" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X55" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y55" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>89.8</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
@@ -7026,32 +7054,36 @@
       </c>
       <c r="F56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G56" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="I56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J56" s="2" t="inlineStr"/>
       <c r="K56" s="2" t="inlineStr"/>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M56" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M56" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N56" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7059,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7083,27 +7115,27 @@
       </c>
       <c r="W56" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X56" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y56" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
@@ -7141,32 +7173,36 @@
       </c>
       <c r="F57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="I57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J57" s="2" t="inlineStr"/>
       <c r="K57" s="2" t="inlineStr"/>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M57" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N57" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7174,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7198,17 +7234,17 @@
       </c>
       <c r="W57" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X57" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y57" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z57" s="2" t="inlineStr">
@@ -7218,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7256,32 +7292,36 @@
       </c>
       <c r="F58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
       <c r="K58" s="2" t="inlineStr"/>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M58" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M58" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N58" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7289,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7313,27 +7353,27 @@
       </c>
       <c r="W58" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X58" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y58" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>5</t>
-        </is>
-      </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
@@ -7404,7 +7444,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7519,7 +7559,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7634,7 +7674,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7688,7 +7728,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7749,7 +7789,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7811,22 +7851,22 @@
       <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>沪A57902D</t>
+          <t>沪A56630D</t>
         </is>
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
           <t>锦带路迎春路（浦东新区办公中心）</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>港城路地铁站</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -7859,12 +7899,12 @@
       <c r="M63" s="2" t="inlineStr"/>
       <c r="N63" s="2" t="inlineStr">
         <is>
-          <t>07:20</t>
+          <t>06:20</t>
         </is>
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>14:20</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7903,22 +7943,1172 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA63" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB63" s="2" t="inlineStr">
+        <is>
+          <t>114.0</t>
+        </is>
+      </c>
+      <c r="AC63" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr"/>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J64" s="2" t="inlineStr"/>
+      <c r="K64" s="2" t="inlineStr"/>
+      <c r="L64" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr"/>
+      <c r="N64" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O64" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P64" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q64" s="2" t="inlineStr"/>
+      <c r="R64" s="2" t="inlineStr"/>
+      <c r="S64" s="2" t="inlineStr"/>
+      <c r="T64" s="2" t="inlineStr"/>
+      <c r="U64" s="2" t="inlineStr">
+        <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W64" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X64" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y64" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA63" s="2" t="inlineStr">
+      <c r="AA64" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB63" s="2" t="inlineStr">
+      <c r="AB64" s="2" t="inlineStr">
         <is>
           <t>91.0</t>
         </is>
       </c>
-      <c r="AC63" s="2" t="inlineStr">
+      <c r="AC64" s="2" t="inlineStr">
         <is>
           <t>14/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr"/>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J65" s="2" t="inlineStr"/>
+      <c r="K65" s="2" t="inlineStr"/>
+      <c r="L65" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M65" s="2" t="inlineStr"/>
+      <c r="N65" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O65" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P65" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q65" s="2" t="inlineStr"/>
+      <c r="R65" s="2" t="inlineStr"/>
+      <c r="S65" s="2" t="inlineStr"/>
+      <c r="T65" s="2" t="inlineStr"/>
+      <c r="U65" s="2" t="inlineStr">
+        <is>
+          <t>15:08</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W65" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X65" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y65" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z65" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB65" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC65" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr"/>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J66" s="2" t="inlineStr"/>
+      <c r="K66" s="2" t="inlineStr"/>
+      <c r="L66" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M66" s="2" t="inlineStr"/>
+      <c r="N66" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O66" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P66" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q66" s="2" t="inlineStr"/>
+      <c r="R66" s="2" t="inlineStr"/>
+      <c r="S66" s="2" t="inlineStr"/>
+      <c r="T66" s="2" t="inlineStr"/>
+      <c r="U66" s="2" t="inlineStr">
+        <is>
+          <t>15:10</t>
+        </is>
+      </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W66" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X66" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y66" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z66" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA66" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB66" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC66" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr"/>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O67" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P67" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q67" s="2" t="inlineStr"/>
+      <c r="R67" s="2" t="inlineStr"/>
+      <c r="S67" s="2" t="inlineStr"/>
+      <c r="T67" s="2" t="inlineStr"/>
+      <c r="U67" s="2" t="inlineStr">
+        <is>
+          <t>15:15</t>
+        </is>
+      </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W67" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X67" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y67" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z67" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA67" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB67" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC67" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr"/>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="inlineStr"/>
+      <c r="K68" s="2" t="inlineStr"/>
+      <c r="L68" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr"/>
+      <c r="N68" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O68" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P68" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q68" s="2" t="inlineStr"/>
+      <c r="R68" s="2" t="inlineStr"/>
+      <c r="S68" s="2" t="inlineStr"/>
+      <c r="T68" s="2" t="inlineStr"/>
+      <c r="U68" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W68" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X68" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y68" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z68" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB68" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC68" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr"/>
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J69" s="2" t="inlineStr"/>
+      <c r="K69" s="2" t="inlineStr"/>
+      <c r="L69" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr"/>
+      <c r="N69" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O69" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P69" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q69" s="2" t="inlineStr"/>
+      <c r="R69" s="2" t="inlineStr"/>
+      <c r="S69" s="2" t="inlineStr"/>
+      <c r="T69" s="2" t="inlineStr"/>
+      <c r="U69" s="2" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W69" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X69" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y69" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z69" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA69" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB69" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC69" s="2" t="inlineStr">
+        <is>
+          <t>7/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr"/>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="inlineStr"/>
+      <c r="K70" s="2" t="inlineStr"/>
+      <c r="L70" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr"/>
+      <c r="N70" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O70" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P70" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q70" s="2" t="inlineStr"/>
+      <c r="R70" s="2" t="inlineStr"/>
+      <c r="S70" s="2" t="inlineStr"/>
+      <c r="T70" s="2" t="inlineStr"/>
+      <c r="U70" s="2" t="inlineStr">
+        <is>
+          <t>15:45</t>
+        </is>
+      </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W70" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X70" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y70" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z70" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB70" s="2" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="AC70" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr"/>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J71" s="2" t="inlineStr"/>
+      <c r="K71" s="2" t="inlineStr"/>
+      <c r="L71" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr"/>
+      <c r="N71" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O71" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P71" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q71" s="2" t="inlineStr"/>
+      <c r="R71" s="2" t="inlineStr"/>
+      <c r="S71" s="2" t="inlineStr"/>
+      <c r="T71" s="2" t="inlineStr"/>
+      <c r="U71" s="2" t="inlineStr">
+        <is>
+          <t>15:50</t>
+        </is>
+      </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W71" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X71" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y71" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z71" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB71" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC71" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr"/>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J72" s="2" t="inlineStr"/>
+      <c r="K72" s="2" t="inlineStr"/>
+      <c r="L72" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr"/>
+      <c r="N72" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O72" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P72" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q72" s="2" t="inlineStr"/>
+      <c r="R72" s="2" t="inlineStr"/>
+      <c r="S72" s="2" t="inlineStr"/>
+      <c r="T72" s="2" t="inlineStr"/>
+      <c r="U72" s="2" t="inlineStr">
+        <is>
+          <t>15:55</t>
+        </is>
+      </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W72" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X72" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y72" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z72" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA72" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB72" s="2" t="inlineStr">
+        <is>
+          <t>83.5</t>
+        </is>
+      </c>
+      <c r="AC72" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr"/>
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G73" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J73" s="2" t="inlineStr"/>
+      <c r="K73" s="2" t="inlineStr"/>
+      <c r="L73" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr"/>
+      <c r="N73" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O73" s="2" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
+      <c r="P73" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q73" s="2" t="inlineStr"/>
+      <c r="R73" s="2" t="inlineStr"/>
+      <c r="S73" s="2" t="inlineStr"/>
+      <c r="T73" s="2" t="inlineStr"/>
+      <c r="U73" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>86.0</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>3/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC73"/>
+  <dimension ref="A1:AC81"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,7 +938,7 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1424,12 +1424,12 @@
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1529,22 +1529,22 @@
       </c>
       <c r="Z9" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,22 +1886,22 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA12" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA12" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2362,7 +2362,7 @@
       </c>
       <c r="Z16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA16" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,7 +2715,7 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3439,12 +3439,12 @@
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3663,22 +3663,22 @@
       </c>
       <c r="Z27" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,22 +4139,22 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA31" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA31" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4377,7 +4377,7 @@
       </c>
       <c r="Z33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA33" s="2" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5109,12 +5109,12 @@
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5218,22 +5218,22 @@
       </c>
       <c r="Z40" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5266,7 +5266,7 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq30，推进5站，达到≥2站确认条件</t>
+          <t>原方向在全程44%处后消失；随后反向物理轨迹由seq25推进至seq39，推进14站，达到≥2站确认条件</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,22 +5583,22 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA43" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA43" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5702,7 +5702,7 @@
       </c>
       <c r="Z44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA44" s="2" t="inlineStr">
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,7 +6178,7 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6307,12 +6307,12 @@
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6416,22 +6416,22 @@
       </c>
       <c r="Z50" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,22 +6654,22 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA52" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA52" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6773,7 +6773,7 @@
       </c>
       <c r="Z53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA53" s="2" t="inlineStr">
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,7 +7249,7 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7302,12 +7302,12 @@
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>15:47</t>
         </is>
       </c>
       <c r="I58" s="2" t="inlineStr">
         <is>
-          <t>86分钟</t>
+          <t>87分钟</t>
         </is>
       </c>
       <c r="J58" s="2" t="inlineStr"/>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.0</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7411,32 +7411,36 @@
       </c>
       <c r="F59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G59" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>15:44</t>
         </is>
       </c>
       <c r="I59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J59" s="2" t="inlineStr"/>
       <c r="K59" s="2" t="inlineStr"/>
       <c r="L59" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M59" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M59" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N59" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -7444,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7468,37 +7472,37 @@
       </c>
       <c r="W59" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X59" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y59" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7526,32 +7530,36 @@
       </c>
       <c r="F60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>92分钟</t>
         </is>
       </c>
       <c r="J60" s="2" t="inlineStr"/>
       <c r="K60" s="2" t="inlineStr"/>
       <c r="L60" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M60" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M60" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N60" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -7559,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7583,37 +7591,37 @@
       </c>
       <c r="W60" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X60" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y60" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z60" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>84.5</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7641,32 +7649,36 @@
       </c>
       <c r="F61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G61" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="I61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J61" s="2" t="inlineStr"/>
       <c r="K61" s="2" t="inlineStr"/>
       <c r="L61" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M61" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M61" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N61" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7674,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:01</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7698,17 +7710,17 @@
       </c>
       <c r="W61" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X61" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y61" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z61" s="2" t="inlineStr">
@@ -7718,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.4</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7756,32 +7768,36 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:21</t>
         </is>
       </c>
       <c r="I62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J62" s="2" t="inlineStr"/>
       <c r="K62" s="2" t="inlineStr"/>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M62" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M62" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N62" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -7789,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7813,37 +7829,37 @@
       </c>
       <c r="W62" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X62" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y62" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA62" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA62" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>90.2</t>
+          <t>90.4</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7871,32 +7887,36 @@
       </c>
       <c r="F63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="I63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J63" s="2" t="inlineStr"/>
       <c r="K63" s="2" t="inlineStr"/>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M63" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M63" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N63" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -7904,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7928,32 +7948,32 @@
       </c>
       <c r="W63" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X63" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y63" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -7986,32 +8006,36 @@
       </c>
       <c r="F64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:13</t>
         </is>
       </c>
       <c r="I64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>73分钟</t>
         </is>
       </c>
       <c r="J64" s="2" t="inlineStr"/>
       <c r="K64" s="2" t="inlineStr"/>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M64" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N64" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -8019,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8043,37 +8067,37 @@
       </c>
       <c r="W64" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X64" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y64" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>82.0</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8134,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8173,7 +8197,7 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
@@ -8188,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8249,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8364,7 +8388,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8403,7 +8427,7 @@
       </c>
       <c r="Z67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA67" s="2" t="inlineStr">
@@ -8418,7 +8442,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8479,7 +8503,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8533,7 +8557,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8618,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8648,7 +8672,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8709,7 +8733,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8763,7 +8787,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8824,7 +8848,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8878,7 +8902,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8963,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9001,22 +9025,22 @@
       <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
-          <t>沪A35172D</t>
+          <t>沪A36809D</t>
         </is>
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
+        <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="E73" s="2" t="inlineStr">
+        <is>
           <t>港城路地铁站</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
-        <is>
-          <t>16:10</t>
-        </is>
-      </c>
-      <c r="E73" s="2" t="inlineStr">
-        <is>
-          <t>锦带路迎春路（浦东新区办公中心）</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -9049,12 +9073,12 @@
       <c r="M73" s="2" t="inlineStr"/>
       <c r="N73" s="2" t="inlineStr">
         <is>
-          <t>06:30</t>
+          <t>06:01</t>
         </is>
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9068,47 +9092,967 @@
       <c r="T73" s="2" t="inlineStr"/>
       <c r="U73" s="2" t="inlineStr">
         <is>
+          <t>16:05</t>
+        </is>
+      </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W73" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X73" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y73" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z73" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA73" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB73" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC73" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr"/>
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
           <t>16:10</t>
         </is>
       </c>
-      <c r="V73" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I74" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J74" s="2" t="inlineStr"/>
+      <c r="K74" s="2" t="inlineStr"/>
+      <c r="L74" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
+      <c r="N74" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O74" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P74" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q74" s="2" t="inlineStr"/>
+      <c r="R74" s="2" t="inlineStr"/>
+      <c r="S74" s="2" t="inlineStr"/>
+      <c r="T74" s="2" t="inlineStr"/>
+      <c r="U74" s="2" t="inlineStr">
+        <is>
+          <t>16:10</t>
+        </is>
+      </c>
+      <c r="V74" s="2" t="inlineStr">
         <is>
           <t>计划发车</t>
         </is>
       </c>
-      <c r="W73" s="2" t="inlineStr">
+      <c r="W74" s="2" t="inlineStr">
         <is>
           <t>D</t>
         </is>
       </c>
-      <c r="X73" s="2" t="inlineStr">
+      <c r="X74" s="2" t="inlineStr">
         <is>
           <t>待确认</t>
         </is>
       </c>
-      <c r="Y73" s="2" t="inlineStr">
+      <c r="Y74" s="2" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
-      <c r="Z73" s="2" t="inlineStr">
+      <c r="Z74" s="2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA73" s="2" t="inlineStr">
+      <c r="AA74" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB73" s="2" t="inlineStr">
-        <is>
-          <t>86.0</t>
-        </is>
-      </c>
-      <c r="AC73" s="2" t="inlineStr">
+      <c r="AB74" s="2" t="inlineStr">
+        <is>
+          <t>86.2</t>
+        </is>
+      </c>
+      <c r="AC74" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr"/>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J75" s="2" t="inlineStr"/>
+      <c r="K75" s="2" t="inlineStr"/>
+      <c r="L75" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr"/>
+      <c r="N75" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O75" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P75" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q75" s="2" t="inlineStr"/>
+      <c r="R75" s="2" t="inlineStr"/>
+      <c r="S75" s="2" t="inlineStr"/>
+      <c r="T75" s="2" t="inlineStr"/>
+      <c r="U75" s="2" t="inlineStr">
+        <is>
+          <t>16:15</t>
+        </is>
+      </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W75" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X75" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y75" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z75" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA75" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB75" s="2" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="AC75" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr"/>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>沪A35591D</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E76" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G76" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J76" s="2" t="inlineStr"/>
+      <c r="K76" s="2" t="inlineStr"/>
+      <c r="L76" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr"/>
+      <c r="N76" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O76" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P76" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q76" s="2" t="inlineStr"/>
+      <c r="R76" s="2" t="inlineStr"/>
+      <c r="S76" s="2" t="inlineStr"/>
+      <c r="T76" s="2" t="inlineStr"/>
+      <c r="U76" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W76" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X76" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y76" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z76" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA76" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB76" s="2" t="inlineStr">
+        <is>
+          <t>84.5</t>
+        </is>
+      </c>
+      <c r="AC76" s="2" t="inlineStr">
         <is>
           <t>3/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr"/>
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="E77" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G77" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J77" s="2" t="inlineStr"/>
+      <c r="K77" s="2" t="inlineStr"/>
+      <c r="L77" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr"/>
+      <c r="N77" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O77" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P77" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q77" s="2" t="inlineStr"/>
+      <c r="R77" s="2" t="inlineStr"/>
+      <c r="S77" s="2" t="inlineStr"/>
+      <c r="T77" s="2" t="inlineStr"/>
+      <c r="U77" s="2" t="inlineStr">
+        <is>
+          <t>16:25</t>
+        </is>
+      </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W77" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X77" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y77" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z77" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB77" s="2" t="inlineStr">
+        <is>
+          <t>82.0</t>
+        </is>
+      </c>
+      <c r="AC77" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr"/>
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E78" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G78" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J78" s="2" t="inlineStr"/>
+      <c r="K78" s="2" t="inlineStr"/>
+      <c r="L78" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr"/>
+      <c r="N78" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O78" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P78" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q78" s="2" t="inlineStr"/>
+      <c r="R78" s="2" t="inlineStr"/>
+      <c r="S78" s="2" t="inlineStr"/>
+      <c r="T78" s="2" t="inlineStr"/>
+      <c r="U78" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W78" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X78" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y78" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z78" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA78" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB78" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC78" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr"/>
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="E79" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G79" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J79" s="2" t="inlineStr"/>
+      <c r="K79" s="2" t="inlineStr"/>
+      <c r="L79" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M79" s="2" t="inlineStr"/>
+      <c r="N79" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O79" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P79" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q79" s="2" t="inlineStr"/>
+      <c r="R79" s="2" t="inlineStr"/>
+      <c r="S79" s="2" t="inlineStr"/>
+      <c r="T79" s="2" t="inlineStr"/>
+      <c r="U79" s="2" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W79" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X79" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y79" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z79" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA79" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB79" s="2" t="inlineStr">
+        <is>
+          <t>90.4</t>
+        </is>
+      </c>
+      <c r="AC79" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr"/>
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>沪A55207D</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="E80" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G80" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J80" s="2" t="inlineStr"/>
+      <c r="K80" s="2" t="inlineStr"/>
+      <c r="L80" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr"/>
+      <c r="N80" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O80" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P80" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q80" s="2" t="inlineStr"/>
+      <c r="R80" s="2" t="inlineStr"/>
+      <c r="S80" s="2" t="inlineStr"/>
+      <c r="T80" s="2" t="inlineStr"/>
+      <c r="U80" s="2" t="inlineStr">
+        <is>
+          <t>16:55</t>
+        </is>
+      </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W80" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X80" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y80" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z80" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA80" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB80" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC80" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr"/>
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="E81" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G81" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J81" s="2" t="inlineStr"/>
+      <c r="K81" s="2" t="inlineStr"/>
+      <c r="L81" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr"/>
+      <c r="N81" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O81" s="2" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
+      <c r="P81" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q81" s="2" t="inlineStr"/>
+      <c r="R81" s="2" t="inlineStr"/>
+      <c r="S81" s="2" t="inlineStr"/>
+      <c r="T81" s="2" t="inlineStr"/>
+      <c r="U81" s="2" t="inlineStr">
+        <is>
+          <t>16:57</t>
+        </is>
+      </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W81" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X81" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y81" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z81" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA81" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB81" s="2" t="inlineStr">
+        <is>
+          <t>101.0</t>
+        </is>
+      </c>
+      <c r="AC81" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC81"/>
+  <dimension ref="A1:AC89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -823,22 +823,22 @@
       </c>
       <c r="Z3" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA3" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA3" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="Z5" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA5" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,22 +1295,22 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1414,22 +1414,22 @@
       </c>
       <c r="Z8" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA8" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA8" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="Z14" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA14" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA14" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2730,7 +2730,7 @@
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2834,22 +2834,22 @@
       </c>
       <c r="Z20" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA20" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA20" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2953,22 +2953,22 @@
       </c>
       <c r="Z21" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA21" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA21" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,22 +3191,22 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3429,22 +3429,22 @@
       </c>
       <c r="Z25" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA25" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA25" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4258,22 +4258,22 @@
       </c>
       <c r="Z32" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA32" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA32" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4615,22 +4615,22 @@
       </c>
       <c r="Z35" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA35" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA35" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4734,22 +4734,22 @@
       </c>
       <c r="Z36" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA36" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA36" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,22 +4980,22 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5099,22 +5099,22 @@
       </c>
       <c r="Z39" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA39" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA39" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5821,22 +5821,22 @@
       </c>
       <c r="Z45" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA45" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA45" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5940,22 +5940,22 @@
       </c>
       <c r="Z46" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA46" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA46" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6059,22 +6059,22 @@
       </c>
       <c r="Z47" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA47" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA47" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6297,22 +6297,22 @@
       </c>
       <c r="Z49" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA49" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA49" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6892,22 +6892,22 @@
       </c>
       <c r="Z54" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA54" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA54" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7011,22 +7011,22 @@
       </c>
       <c r="Z55" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA55" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA55" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7130,22 +7130,22 @@
       </c>
       <c r="Z56" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA56" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA56" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7368,22 +7368,22 @@
       </c>
       <c r="Z58" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA58" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA58" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>16:01</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8212,7 +8212,7 @@
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8355,32 +8355,36 @@
       </c>
       <c r="F67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G67" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:39</t>
         </is>
       </c>
       <c r="I67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J67" s="2" t="inlineStr"/>
       <c r="K67" s="2" t="inlineStr"/>
       <c r="L67" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M67" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M67" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N67" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8388,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8412,17 +8416,17 @@
       </c>
       <c r="W67" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X67" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y67" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z67" s="2" t="inlineStr">
@@ -8432,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8470,32 +8474,36 @@
       </c>
       <c r="F68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J68" s="2" t="inlineStr"/>
       <c r="K68" s="2" t="inlineStr"/>
       <c r="L68" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M68" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M68" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N68" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -8503,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8527,37 +8535,37 @@
       </c>
       <c r="W68" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X68" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y68" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z68" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA68" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AA68" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>86.8</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8585,32 +8593,36 @@
       </c>
       <c r="F69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>16:50</t>
         </is>
       </c>
       <c r="I69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J69" s="2" t="inlineStr"/>
       <c r="K69" s="2" t="inlineStr"/>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M69" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M69" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N69" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8618,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8642,37 +8654,37 @@
       </c>
       <c r="W69" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X69" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y69" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>84.3</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -8700,32 +8712,36 @@
       </c>
       <c r="F70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:04</t>
         </is>
       </c>
       <c r="I70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J70" s="2" t="inlineStr"/>
       <c r="K70" s="2" t="inlineStr"/>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M70" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M70" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N70" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -8733,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8757,37 +8773,37 @@
       </c>
       <c r="W70" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X70" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y70" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z70" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA70" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA70" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8815,32 +8831,36 @@
       </c>
       <c r="F71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="I71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>91分钟</t>
         </is>
       </c>
       <c r="J71" s="2" t="inlineStr"/>
       <c r="K71" s="2" t="inlineStr"/>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M71" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M71" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N71" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -8848,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8872,37 +8892,37 @@
       </c>
       <c r="W71" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X71" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y71" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z71" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA71" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA71" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8930,32 +8950,36 @@
       </c>
       <c r="F72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G72" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:25</t>
         </is>
       </c>
       <c r="I72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J72" s="2" t="inlineStr"/>
       <c r="K72" s="2" t="inlineStr"/>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M72" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M72" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N72" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -8963,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -8987,37 +9011,37 @@
       </c>
       <c r="W72" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X72" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y72" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>85.7</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9078,7 +9102,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9132,7 +9156,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9160,32 +9184,36 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9193,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9217,37 +9245,37 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA74" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="AA74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>88.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9336,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9362,7 +9390,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9451,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9538,7 +9566,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9653,7 +9681,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9707,7 +9735,7 @@
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9768,7 +9796,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9883,7 +9911,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9927,17 +9955,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -9998,7 +10026,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10056,6 +10084,926 @@
         </is>
       </c>
     </row>
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr"/>
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="E82" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G82" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J82" s="2" t="inlineStr"/>
+      <c r="K82" s="2" t="inlineStr"/>
+      <c r="L82" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr"/>
+      <c r="N82" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O82" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P82" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q82" s="2" t="inlineStr"/>
+      <c r="R82" s="2" t="inlineStr"/>
+      <c r="S82" s="2" t="inlineStr"/>
+      <c r="T82" s="2" t="inlineStr"/>
+      <c r="U82" s="2" t="inlineStr">
+        <is>
+          <t>17:10</t>
+        </is>
+      </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W82" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X82" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y82" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z82" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA82" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB82" s="2" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="AC82" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr"/>
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="E83" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G83" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J83" s="2" t="inlineStr"/>
+      <c r="K83" s="2" t="inlineStr"/>
+      <c r="L83" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr"/>
+      <c r="N83" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O83" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P83" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q83" s="2" t="inlineStr"/>
+      <c r="R83" s="2" t="inlineStr"/>
+      <c r="S83" s="2" t="inlineStr"/>
+      <c r="T83" s="2" t="inlineStr"/>
+      <c r="U83" s="2" t="inlineStr">
+        <is>
+          <t>17:15</t>
+        </is>
+      </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W83" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X83" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y83" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z83" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA83" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB83" s="2" t="inlineStr">
+        <is>
+          <t>96.5</t>
+        </is>
+      </c>
+      <c r="AC83" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr"/>
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="E84" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G84" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J84" s="2" t="inlineStr"/>
+      <c r="K84" s="2" t="inlineStr"/>
+      <c r="L84" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M84" s="2" t="inlineStr"/>
+      <c r="N84" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O84" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P84" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q84" s="2" t="inlineStr"/>
+      <c r="R84" s="2" t="inlineStr"/>
+      <c r="S84" s="2" t="inlineStr"/>
+      <c r="T84" s="2" t="inlineStr"/>
+      <c r="U84" s="2" t="inlineStr">
+        <is>
+          <t>17:25</t>
+        </is>
+      </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W84" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X84" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y84" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z84" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA84" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB84" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC84" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr"/>
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>沪A55150D</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="E85" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G85" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J85" s="2" t="inlineStr"/>
+      <c r="K85" s="2" t="inlineStr"/>
+      <c r="L85" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr"/>
+      <c r="N85" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O85" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P85" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q85" s="2" t="inlineStr"/>
+      <c r="R85" s="2" t="inlineStr"/>
+      <c r="S85" s="2" t="inlineStr"/>
+      <c r="T85" s="2" t="inlineStr"/>
+      <c r="U85" s="2" t="inlineStr">
+        <is>
+          <t>17:30</t>
+        </is>
+      </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W85" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X85" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y85" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z85" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB85" s="2" t="inlineStr">
+        <is>
+          <t>86.8</t>
+        </is>
+      </c>
+      <c r="AC85" s="2" t="inlineStr">
+        <is>
+          <t>8/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr"/>
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>沪A57022D</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="E86" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G86" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J86" s="2" t="inlineStr"/>
+      <c r="K86" s="2" t="inlineStr"/>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr"/>
+      <c r="N86" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O86" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P86" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q86" s="2" t="inlineStr"/>
+      <c r="R86" s="2" t="inlineStr"/>
+      <c r="S86" s="2" t="inlineStr"/>
+      <c r="T86" s="2" t="inlineStr"/>
+      <c r="U86" s="2" t="inlineStr">
+        <is>
+          <t>17:42</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W86" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X86" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y86" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z86" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA86" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB86" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC86" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr"/>
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>沪A61166D</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="E87" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G87" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J87" s="2" t="inlineStr"/>
+      <c r="K87" s="2" t="inlineStr"/>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr"/>
+      <c r="N87" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O87" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P87" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q87" s="2" t="inlineStr"/>
+      <c r="R87" s="2" t="inlineStr"/>
+      <c r="S87" s="2" t="inlineStr"/>
+      <c r="T87" s="2" t="inlineStr"/>
+      <c r="U87" s="2" t="inlineStr">
+        <is>
+          <t>17:50</t>
+        </is>
+      </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W87" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X87" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y87" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z87" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA87" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB87" s="2" t="inlineStr">
+        <is>
+          <t>87.0</t>
+        </is>
+      </c>
+      <c r="AC87" s="2" t="inlineStr">
+        <is>
+          <t>9/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr"/>
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="E88" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G88" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J88" s="2" t="inlineStr"/>
+      <c r="K88" s="2" t="inlineStr"/>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr"/>
+      <c r="N88" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O88" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P88" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q88" s="2" t="inlineStr"/>
+      <c r="R88" s="2" t="inlineStr"/>
+      <c r="S88" s="2" t="inlineStr"/>
+      <c r="T88" s="2" t="inlineStr"/>
+      <c r="U88" s="2" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W88" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X88" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y88" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA88" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB88" s="2" t="inlineStr">
+        <is>
+          <t>85.7</t>
+        </is>
+      </c>
+      <c r="AC88" s="2" t="inlineStr">
+        <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr"/>
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>沪A35172D</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="E89" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G89" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J89" s="2" t="inlineStr"/>
+      <c r="K89" s="2" t="inlineStr"/>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr"/>
+      <c r="N89" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O89" s="2" t="inlineStr">
+        <is>
+          <t>17:20</t>
+        </is>
+      </c>
+      <c r="P89" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q89" s="2" t="inlineStr"/>
+      <c r="R89" s="2" t="inlineStr"/>
+      <c r="S89" s="2" t="inlineStr"/>
+      <c r="T89" s="2" t="inlineStr"/>
+      <c r="U89" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W89" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X89" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y89" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z89" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA89" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB89" s="2" t="inlineStr">
+        <is>
+          <t>88.2</t>
+        </is>
+      </c>
+      <c r="AC89" s="2" t="inlineStr">
+        <is>
+          <t>12/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC89"/>
+  <dimension ref="A1:AC95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -938,22 +938,22 @@
       </c>
       <c r="Z4" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1310,7 +1310,7 @@
       </c>
       <c r="AC7" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1490,7 +1490,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
@@ -1534,17 +1534,17 @@
       </c>
       <c r="AA9" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB9" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1782,7 +1782,7 @@
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="Z12" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA12" s="2" t="inlineStr">
@@ -1901,7 +1901,7 @@
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="Z13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA13" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2243,22 +2243,22 @@
       </c>
       <c r="Z15" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA15" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA15" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2367,17 +2367,17 @@
       </c>
       <c r="AA16" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2715,22 +2715,22 @@
       </c>
       <c r="Z19" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3206,7 +3206,7 @@
       </c>
       <c r="AC23" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3310,22 +3310,22 @@
       </c>
       <c r="Z24" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3624,7 +3624,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -3668,17 +3668,17 @@
       </c>
       <c r="AA27" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB27" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3797,7 +3797,7 @@
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,12 +3906,12 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4020,7 +4020,7 @@
       </c>
       <c r="Z30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA30" s="2" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4139,7 +4139,7 @@
       </c>
       <c r="Z31" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA31" s="2" t="inlineStr">
@@ -4154,7 +4154,7 @@
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4382,17 +4382,17 @@
       </c>
       <c r="AA33" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4853,22 +4853,22 @@
       </c>
       <c r="Z37" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="AC38" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5179,7 +5179,7 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
@@ -5223,17 +5223,17 @@
       </c>
       <c r="AA40" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB40" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5360,7 +5360,7 @@
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5464,7 +5464,7 @@
       </c>
       <c r="Z42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA42" s="2" t="inlineStr">
@@ -5479,7 +5479,7 @@
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5583,7 +5583,7 @@
       </c>
       <c r="Z43" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA43" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5707,17 +5707,17 @@
       </c>
       <c r="AA44" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6178,22 +6178,22 @@
       </c>
       <c r="Z48" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6377,7 +6377,7 @@
       </c>
       <c r="O50" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P50" s="2" t="inlineStr">
@@ -6421,17 +6421,17 @@
       </c>
       <c r="AA50" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB50" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6535,7 +6535,7 @@
       </c>
       <c r="Z51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA51" s="2" t="inlineStr">
@@ -6550,7 +6550,7 @@
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="Z52" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA52" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6778,17 +6778,17 @@
       </c>
       <c r="AA53" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7249,22 +7249,22 @@
       </c>
       <c r="Z57" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,22 +7487,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7567,7 +7567,7 @@
       </c>
       <c r="O60" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P60" s="2" t="inlineStr">
@@ -7611,17 +7611,17 @@
       </c>
       <c r="AA60" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB60" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7725,7 +7725,7 @@
       </c>
       <c r="Z61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA61" s="2" t="inlineStr">
@@ -7740,7 +7740,7 @@
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7844,7 +7844,7 @@
       </c>
       <c r="Z62" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA62" s="2" t="inlineStr">
@@ -7859,7 +7859,7 @@
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8082,22 +8082,22 @@
       </c>
       <c r="Z64" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA64" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA64" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8197,22 +8197,22 @@
       </c>
       <c r="Z65" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,12 +8317,12 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8436,17 +8436,17 @@
       </c>
       <c r="AA67" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8684,7 +8684,7 @@
       </c>
       <c r="AC69" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9069,32 +9069,36 @@
       </c>
       <c r="F73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G73" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:35</t>
         </is>
       </c>
       <c r="I73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J73" s="2" t="inlineStr"/>
       <c r="K73" s="2" t="inlineStr"/>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M73" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M73" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N73" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9102,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9126,37 +9130,37 @@
       </c>
       <c r="W73" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X73" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y73" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z73" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9184,36 +9188,32 @@
       </c>
       <c r="F74" s="2" t="inlineStr">
         <is>
-          <t>全程车</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="I74" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="J74" s="2" t="inlineStr"/>
       <c r="K74" s="2" t="inlineStr"/>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±5分钟</t>
-        </is>
-      </c>
-      <c r="M74" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M74" s="2" t="inlineStr"/>
       <c r="N74" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9245,17 +9245,17 @@
       </c>
       <c r="W74" s="2" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>D</t>
         </is>
       </c>
       <c r="X74" s="2" t="inlineStr">
         <is>
-          <t>终点ETA确认/一致估算</t>
+          <t>待确认</t>
         </is>
       </c>
       <c r="Y74" s="2" t="inlineStr">
         <is>
-          <t>是</t>
+          <t>否</t>
         </is>
       </c>
       <c r="Z74" s="2" t="inlineStr">
@@ -9265,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9303,32 +9303,36 @@
       </c>
       <c r="F75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G75" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="I75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J75" s="2" t="inlineStr"/>
       <c r="K75" s="2" t="inlineStr"/>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M75" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M75" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N75" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9336,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9360,37 +9364,37 @@
       </c>
       <c r="W75" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X75" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y75" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9418,32 +9422,36 @@
       </c>
       <c r="F76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G76" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="I76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>95分钟</t>
         </is>
       </c>
       <c r="J76" s="2" t="inlineStr"/>
       <c r="K76" s="2" t="inlineStr"/>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M76" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M76" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N76" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -9451,7 +9459,7 @@
       </c>
       <c r="O76" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>17:50</t>
         </is>
       </c>
       <c r="P76" s="2" t="inlineStr">
@@ -9475,17 +9483,17 @@
       </c>
       <c r="W76" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X76" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y76" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z76" s="2" t="inlineStr">
@@ -9495,17 +9503,17 @@
       </c>
       <c r="AA76" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB76" s="2" t="inlineStr">
         <is>
-          <t>84.5</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9533,32 +9541,36 @@
       </c>
       <c r="F77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="I77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J77" s="2" t="inlineStr"/>
       <c r="K77" s="2" t="inlineStr"/>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M77" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M77" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N77" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -9566,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9590,37 +9602,37 @@
       </c>
       <c r="W77" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X77" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y77" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z77" s="2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA77" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AA77" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>82.0</t>
+          <t>88.3</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>1/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9648,32 +9660,36 @@
       </c>
       <c r="F78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G78" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="I78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>102分钟</t>
         </is>
       </c>
       <c r="J78" s="2" t="inlineStr"/>
       <c r="K78" s="2" t="inlineStr"/>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M78" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M78" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N78" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -9681,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9705,37 +9721,37 @@
       </c>
       <c r="W78" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X78" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y78" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z78" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -9796,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9835,7 +9851,7 @@
       </c>
       <c r="Z79" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA79" s="2" t="inlineStr">
@@ -9850,7 +9866,7 @@
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9878,32 +9894,36 @@
       </c>
       <c r="F80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G80" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:47</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>112分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M80" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M80" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N80" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -9911,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9935,17 +9955,17 @@
       </c>
       <c r="W80" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X80" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y80" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z80" s="2" t="inlineStr">
@@ -9955,17 +9975,17 @@
       </c>
       <c r="AA80" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>86.4</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9993,32 +10013,36 @@
       </c>
       <c r="F81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G81" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:43</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>106分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M81" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M81" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N81" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10026,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10050,17 +10074,17 @@
       </c>
       <c r="W81" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X81" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y81" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z81" s="2" t="inlineStr">
@@ -10070,12 +10094,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>102.7</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10141,7 +10165,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10180,7 +10204,7 @@
       </c>
       <c r="Z82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AA82" s="2" t="inlineStr">
@@ -10195,7 +10219,7 @@
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10223,32 +10247,36 @@
       </c>
       <c r="F83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G83" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>98分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M83" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M83" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N83" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10256,7 +10284,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10280,17 +10308,17 @@
       </c>
       <c r="W83" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X83" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y83" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z83" s="2" t="inlineStr">
@@ -10300,12 +10328,12 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>96.5</t>
+          <t>97.0</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10371,7 +10399,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10425,7 +10453,7 @@
       </c>
       <c r="AC84" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>1/18</t>
         </is>
       </c>
     </row>
@@ -10486,7 +10514,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10540,7 +10568,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10629,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10655,7 +10683,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10716,7 +10744,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10770,7 +10798,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -10831,7 +10859,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10885,7 +10913,7 @@
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -10946,7 +10974,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>18:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -10990,17 +11018,707 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>88.2</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
+          <t>5/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr"/>
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>沪A36809D</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="E90" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G90" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J90" s="2" t="inlineStr"/>
+      <c r="K90" s="2" t="inlineStr"/>
+      <c r="L90" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr"/>
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O90" s="2" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
+      <c r="P90" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q90" s="2" t="inlineStr"/>
+      <c r="R90" s="2" t="inlineStr"/>
+      <c r="S90" s="2" t="inlineStr"/>
+      <c r="T90" s="2" t="inlineStr"/>
+      <c r="U90" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W90" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X90" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y90" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z90" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA90" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB90" s="2" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="AC90" s="2" t="inlineStr">
+        <is>
+          <t>11/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr"/>
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>沪A57902D</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="E91" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G91" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J91" s="2" t="inlineStr"/>
+      <c r="K91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr"/>
+      <c r="N91" s="2" t="inlineStr">
+        <is>
+          <t>07:20</t>
+        </is>
+      </c>
+      <c r="O91" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P91" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q91" s="2" t="inlineStr"/>
+      <c r="R91" s="2" t="inlineStr"/>
+      <c r="S91" s="2" t="inlineStr"/>
+      <c r="T91" s="2" t="inlineStr"/>
+      <c r="U91" s="2" t="inlineStr">
+        <is>
+          <t>18:35</t>
+        </is>
+      </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W91" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X91" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y91" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z91" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA91" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB91" s="2" t="inlineStr">
+        <is>
+          <t>88.3</t>
+        </is>
+      </c>
+      <c r="AC91" s="2" t="inlineStr">
+        <is>
+          <t>10/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr"/>
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="E92" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G92" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J92" s="2" t="inlineStr"/>
+      <c r="K92" s="2" t="inlineStr"/>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr"/>
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O92" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P92" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q92" s="2" t="inlineStr"/>
+      <c r="R92" s="2" t="inlineStr"/>
+      <c r="S92" s="2" t="inlineStr"/>
+      <c r="T92" s="2" t="inlineStr"/>
+      <c r="U92" s="2" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W92" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X92" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y92" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z92" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB92" s="2" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="AC92" s="2" t="inlineStr">
+        <is>
           <t>12/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr"/>
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>沪A53629D</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="E93" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G93" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J93" s="2" t="inlineStr"/>
+      <c r="K93" s="2" t="inlineStr"/>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr"/>
+      <c r="N93" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O93" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P93" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q93" s="2" t="inlineStr"/>
+      <c r="R93" s="2" t="inlineStr"/>
+      <c r="S93" s="2" t="inlineStr"/>
+      <c r="T93" s="2" t="inlineStr"/>
+      <c r="U93" s="2" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W93" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X93" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y93" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z93" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AA93" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB93" s="2" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="AC93" s="2" t="inlineStr">
+        <is>
+          <t>15/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr"/>
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>沪A56123D</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="E94" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G94" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J94" s="2" t="inlineStr"/>
+      <c r="K94" s="2" t="inlineStr"/>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr"/>
+      <c r="N94" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O94" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P94" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q94" s="2" t="inlineStr"/>
+      <c r="R94" s="2" t="inlineStr"/>
+      <c r="S94" s="2" t="inlineStr"/>
+      <c r="T94" s="2" t="inlineStr"/>
+      <c r="U94" s="2" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W94" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X94" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y94" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z94" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA94" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB94" s="2" t="inlineStr">
+        <is>
+          <t>90.4</t>
+        </is>
+      </c>
+      <c r="AC94" s="2" t="inlineStr">
+        <is>
+          <t>13/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr"/>
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>沪A35186D</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="E95" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G95" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J95" s="2" t="inlineStr"/>
+      <c r="K95" s="2" t="inlineStr"/>
+      <c r="L95" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr"/>
+      <c r="N95" s="2" t="inlineStr">
+        <is>
+          <t>07:01</t>
+        </is>
+      </c>
+      <c r="O95" s="2" t="inlineStr">
+        <is>
+          <t>18:20</t>
+        </is>
+      </c>
+      <c r="P95" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q95" s="2" t="inlineStr"/>
+      <c r="R95" s="2" t="inlineStr"/>
+      <c r="S95" s="2" t="inlineStr"/>
+      <c r="T95" s="2" t="inlineStr"/>
+      <c r="U95" s="2" t="inlineStr">
+        <is>
+          <t>19:25</t>
+        </is>
+      </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W95" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X95" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y95" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z95" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AA95" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>85.4</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>2/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC95"/>
+  <dimension ref="A1:AC99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -719,7 +719,7 @@
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -784,7 +784,7 @@
       </c>
       <c r="O3" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P3" s="2" t="inlineStr">
@@ -828,17 +828,17 @@
       </c>
       <c r="AA3" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB3" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -953,7 +953,7 @@
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1062,17 +1062,17 @@
       </c>
       <c r="AA5" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB5" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,7 +1176,7 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>102.7</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1295,7 +1295,7 @@
       </c>
       <c r="Z7" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1658,7 +1658,7 @@
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1767,22 +1767,22 @@
       </c>
       <c r="Z11" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,17 +2010,17 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="AA14" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB14" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2258,7 +2258,7 @@
       </c>
       <c r="AC15" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -2323,7 +2323,7 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
@@ -2372,7 +2372,7 @@
       </c>
       <c r="AB16" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC16" s="2" t="inlineStr">
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -2839,17 +2839,17 @@
       </c>
       <c r="AA20" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB20" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="AA21" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB21" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3191,7 +3191,7 @@
       </c>
       <c r="Z23" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3325,7 +3325,7 @@
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,7 +3544,7 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
@@ -3554,7 +3554,7 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>102.7</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3782,22 +3782,22 @@
       </c>
       <c r="Z28" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3911,7 +3911,7 @@
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,17 +4025,17 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4219,7 +4219,7 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
@@ -4263,17 +4263,17 @@
       </c>
       <c r="AA32" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB32" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -4338,7 +4338,7 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
@@ -4387,7 +4387,7 @@
       </c>
       <c r="AB33" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC33" s="2" t="inlineStr">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -4576,7 +4576,7 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
@@ -4620,17 +4620,17 @@
       </c>
       <c r="AA35" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB35" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4739,17 +4739,17 @@
       </c>
       <c r="AA36" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB36" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4868,7 +4868,7 @@
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4980,7 +4980,7 @@
       </c>
       <c r="Z38" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5345,22 +5345,22 @@
       </c>
       <c r="Z41" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,17 +5469,17 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5663,7 +5663,7 @@
       </c>
       <c r="O44" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P44" s="2" t="inlineStr">
@@ -5712,7 +5712,7 @@
       </c>
       <c r="AB44" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC44" s="2" t="inlineStr">
@@ -5782,7 +5782,7 @@
       </c>
       <c r="O45" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P45" s="2" t="inlineStr">
@@ -5826,17 +5826,17 @@
       </c>
       <c r="AA45" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB45" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5901,7 +5901,7 @@
       </c>
       <c r="O46" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P46" s="2" t="inlineStr">
@@ -5945,17 +5945,17 @@
       </c>
       <c r="AA46" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB46" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6064,17 +6064,17 @@
       </c>
       <c r="AA47" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB47" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6193,7 +6193,7 @@
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,17 +6540,17 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="O53" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P53" s="2" t="inlineStr">
@@ -6783,7 +6783,7 @@
       </c>
       <c r="AB53" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC53" s="2" t="inlineStr">
@@ -6853,7 +6853,7 @@
       </c>
       <c r="O54" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P54" s="2" t="inlineStr">
@@ -6897,17 +6897,17 @@
       </c>
       <c r="AA54" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB54" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6972,7 +6972,7 @@
       </c>
       <c r="O55" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P55" s="2" t="inlineStr">
@@ -7016,17 +7016,17 @@
       </c>
       <c r="AA55" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB55" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7135,17 +7135,17 @@
       </c>
       <c r="AA56" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB56" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7264,7 +7264,7 @@
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7502,7 +7502,7 @@
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,17 +7730,17 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,7 +7963,7 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>102.7</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="AC64" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8322,7 +8322,7 @@
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
@@ -8392,7 +8392,7 @@
       </c>
       <c r="O67" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P67" s="2" t="inlineStr">
@@ -8441,7 +8441,7 @@
       </c>
       <c r="AB67" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC67" s="2" t="inlineStr">
@@ -8511,7 +8511,7 @@
       </c>
       <c r="O68" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P68" s="2" t="inlineStr">
@@ -8555,17 +8555,17 @@
       </c>
       <c r="AA68" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB68" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Z69" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA69" s="2" t="inlineStr">
@@ -8749,7 +8749,7 @@
       </c>
       <c r="O70" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P70" s="2" t="inlineStr">
@@ -8793,17 +8793,17 @@
       </c>
       <c r="AA70" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB70" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8912,17 +8912,17 @@
       </c>
       <c r="AA71" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB71" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9026,22 +9026,22 @@
       </c>
       <c r="Z72" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9160,7 +9160,7 @@
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9632,7 +9632,7 @@
       </c>
       <c r="AC77" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9904,24 +9904,24 @@
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>18:47</t>
+          <t>18:49</t>
         </is>
       </c>
       <c r="I80" s="2" t="inlineStr">
         <is>
-          <t>112分钟</t>
+          <t>114分钟</t>
         </is>
       </c>
       <c r="J80" s="2" t="inlineStr"/>
       <c r="K80" s="2" t="inlineStr"/>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
         </is>
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="N80" s="2" t="inlineStr">
@@ -9931,7 +9931,7 @@
       </c>
       <c r="O80" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>18:40</t>
         </is>
       </c>
       <c r="P80" s="2" t="inlineStr">
@@ -9980,7 +9980,7 @@
       </c>
       <c r="AB80" s="2" t="inlineStr">
         <is>
-          <t>90.7</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="AC80" s="2" t="inlineStr">
@@ -10023,24 +10023,24 @@
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>18:43</t>
+          <t>18:41</t>
         </is>
       </c>
       <c r="I81" s="2" t="inlineStr">
         <is>
-          <t>106分钟</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J81" s="2" t="inlineStr"/>
       <c r="K81" s="2" t="inlineStr"/>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N81" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10089,7 +10089,7 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
@@ -10099,7 +10099,7 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>102.7</t>
+          <t>102.0</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10132,32 +10132,36 @@
       </c>
       <c r="F82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J82" s="2" t="inlineStr"/>
       <c r="K82" s="2" t="inlineStr"/>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M82" s="2" t="inlineStr"/>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
+        </is>
+      </c>
+      <c r="M82" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="N82" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -10165,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10189,17 +10193,17 @@
       </c>
       <c r="W82" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X82" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y82" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z82" s="2" t="inlineStr">
@@ -10209,17 +10213,17 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>85.4</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>2/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10257,24 +10261,24 @@
       </c>
       <c r="H83" s="2" t="inlineStr">
         <is>
-          <t>18:53</t>
+          <t>18:51</t>
         </is>
       </c>
       <c r="I83" s="2" t="inlineStr">
         <is>
-          <t>98分钟</t>
+          <t>96分钟</t>
         </is>
       </c>
       <c r="J83" s="2" t="inlineStr"/>
       <c r="K83" s="2" t="inlineStr"/>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N83" s="2" t="inlineStr">
@@ -10284,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10323,7 +10327,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10333,7 +10337,7 @@
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>97.0</t>
+          <t>96.3</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
@@ -10399,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10438,7 +10442,7 @@
       </c>
       <c r="Z84" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA84" s="2" t="inlineStr">
@@ -10481,32 +10485,36 @@
       </c>
       <c r="F85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:14</t>
         </is>
       </c>
       <c r="I85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>104分钟</t>
         </is>
       </c>
       <c r="J85" s="2" t="inlineStr"/>
       <c r="K85" s="2" t="inlineStr"/>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M85" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M85" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N85" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -10514,7 +10522,7 @@
       </c>
       <c r="O85" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P85" s="2" t="inlineStr">
@@ -10538,17 +10546,17 @@
       </c>
       <c r="W85" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X85" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y85" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z85" s="2" t="inlineStr">
@@ -10558,17 +10566,17 @@
       </c>
       <c r="AA85" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB85" s="2" t="inlineStr">
         <is>
-          <t>86.8</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>7/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -10596,32 +10604,36 @@
       </c>
       <c r="F86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G86" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:16</t>
         </is>
       </c>
       <c r="I86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J86" s="2" t="inlineStr"/>
       <c r="K86" s="2" t="inlineStr"/>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M86" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M86" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N86" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -10629,7 +10641,7 @@
       </c>
       <c r="O86" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="P86" s="2" t="inlineStr">
@@ -10653,17 +10665,17 @@
       </c>
       <c r="W86" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X86" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y86" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z86" s="2" t="inlineStr">
@@ -10673,17 +10685,17 @@
       </c>
       <c r="AA86" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB86" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>88.0</t>
         </is>
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -10711,32 +10723,36 @@
       </c>
       <c r="F87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G87" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:31</t>
         </is>
       </c>
       <c r="I87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>101分钟</t>
         </is>
       </c>
       <c r="J87" s="2" t="inlineStr"/>
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M87" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+        </is>
+      </c>
+      <c r="M87" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="N87" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10744,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10768,17 +10784,17 @@
       </c>
       <c r="W87" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X87" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y87" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z87" s="2" t="inlineStr">
@@ -10788,17 +10804,17 @@
       </c>
       <c r="AA87" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB87" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>8/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -10826,32 +10842,36 @@
       </c>
       <c r="F88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G88" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:24</t>
         </is>
       </c>
       <c r="I88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J88" s="2" t="inlineStr"/>
       <c r="K88" s="2" t="inlineStr"/>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M88" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M88" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N88" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -10859,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10883,37 +10903,37 @@
       </c>
       <c r="W88" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X88" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y88" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z88" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>85.7</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>2/18</t>
         </is>
       </c>
     </row>
@@ -10974,7 +10994,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11028,7 +11048,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11089,7 +11109,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11143,7 +11163,7 @@
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>11/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -11204,7 +11224,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11258,7 +11278,7 @@
       </c>
       <c r="AC91" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>8/18</t>
         </is>
       </c>
     </row>
@@ -11319,7 +11339,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11373,7 +11393,7 @@
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11434,7 +11454,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11549,7 +11569,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11664,7 +11684,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>18:20</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11708,15 +11728,475 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB95" s="2" t="inlineStr">
+        <is>
+          <t>88.0</t>
+        </is>
+      </c>
+      <c r="AC95" s="2" t="inlineStr">
+        <is>
+          <t>6/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr"/>
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="E96" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G96" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J96" s="2" t="inlineStr"/>
+      <c r="K96" s="2" t="inlineStr"/>
+      <c r="L96" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr"/>
+      <c r="N96" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O96" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P96" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q96" s="2" t="inlineStr"/>
+      <c r="R96" s="2" t="inlineStr"/>
+      <c r="S96" s="2" t="inlineStr"/>
+      <c r="T96" s="2" t="inlineStr"/>
+      <c r="U96" s="2" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W96" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X96" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y96" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z96" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AB95" s="2" t="inlineStr">
-        <is>
-          <t>85.4</t>
-        </is>
-      </c>
-      <c r="AC95" s="2" t="inlineStr">
+      <c r="AA96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB96" s="2" t="inlineStr">
+        <is>
+          <t>102.0</t>
+        </is>
+      </c>
+      <c r="AC96" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr"/>
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>沪A66391D</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="E97" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G97" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J97" s="2" t="inlineStr"/>
+      <c r="K97" s="2" t="inlineStr"/>
+      <c r="L97" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr"/>
+      <c r="N97" s="2" t="inlineStr">
+        <is>
+          <t>06:30</t>
+        </is>
+      </c>
+      <c r="O97" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P97" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q97" s="2" t="inlineStr"/>
+      <c r="R97" s="2" t="inlineStr"/>
+      <c r="S97" s="2" t="inlineStr"/>
+      <c r="T97" s="2" t="inlineStr"/>
+      <c r="U97" s="2" t="inlineStr">
+        <is>
+          <t>19:50</t>
+        </is>
+      </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W97" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X97" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y97" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z97" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB97" s="2" t="inlineStr">
+        <is>
+          <t>84.3</t>
+        </is>
+      </c>
+      <c r="AC97" s="2" t="inlineStr">
+        <is>
+          <t>1/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr"/>
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="E98" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="F98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G98" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J98" s="2" t="inlineStr"/>
+      <c r="K98" s="2" t="inlineStr"/>
+      <c r="L98" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr"/>
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O98" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P98" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q98" s="2" t="inlineStr"/>
+      <c r="R98" s="2" t="inlineStr"/>
+      <c r="S98" s="2" t="inlineStr"/>
+      <c r="T98" s="2" t="inlineStr"/>
+      <c r="U98" s="2" t="inlineStr">
+        <is>
+          <t>19:58</t>
+        </is>
+      </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W98" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X98" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y98" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA98" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB98" s="2" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="AC98" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr"/>
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>沪A59117D</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="E99" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G99" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J99" s="2" t="inlineStr"/>
+      <c r="K99" s="2" t="inlineStr"/>
+      <c r="L99" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr"/>
+      <c r="N99" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O99" s="2" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="P99" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q99" s="2" t="inlineStr"/>
+      <c r="R99" s="2" t="inlineStr"/>
+      <c r="S99" s="2" t="inlineStr"/>
+      <c r="T99" s="2" t="inlineStr"/>
+      <c r="U99" s="2" t="inlineStr">
+        <is>
+          <t>20:15</t>
+        </is>
+      </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W99" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X99" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y99" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z99" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA99" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB99" s="2" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="AC99" s="2" t="inlineStr">
         <is>
           <t>2/18</t>
         </is>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC99"/>
+  <dimension ref="A1:AC100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -704,22 +704,22 @@
       </c>
       <c r="Z2" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -943,17 +943,17 @@
       </c>
       <c r="AA4" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB4" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -1018,7 +1018,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -1072,7 +1072,7 @@
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="AA8" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB8" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AC14" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2596,22 +2596,22 @@
       </c>
       <c r="Z18" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
@@ -2968,7 +2968,7 @@
       </c>
       <c r="AC21" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3315,17 +3315,17 @@
       </c>
       <c r="AA24" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB24" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC24" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3434,17 +3434,17 @@
       </c>
       <c r="AA25" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB25" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4273,7 +4273,7 @@
       </c>
       <c r="AC32" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
@@ -4749,7 +4749,7 @@
       </c>
       <c r="AC36" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4858,17 +4858,17 @@
       </c>
       <c r="AA37" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB37" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC37" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5104,17 +5104,17 @@
       </c>
       <c r="AA39" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB39" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5836,7 +5836,7 @@
       </c>
       <c r="AC45" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="O47" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P47" s="2" t="inlineStr">
@@ -6074,7 +6074,7 @@
       </c>
       <c r="AC47" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6183,17 +6183,17 @@
       </c>
       <c r="AA48" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB48" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC48" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6302,17 +6302,17 @@
       </c>
       <c r="AA49" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB49" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6907,7 +6907,7 @@
       </c>
       <c r="AC54" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="O56" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P56" s="2" t="inlineStr">
@@ -7145,7 +7145,7 @@
       </c>
       <c r="AC56" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7254,17 +7254,17 @@
       </c>
       <c r="AA57" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB57" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC57" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7373,17 +7373,17 @@
       </c>
       <c r="AA58" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB58" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7487,22 +7487,22 @@
       </c>
       <c r="Z59" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8565,7 +8565,7 @@
       </c>
       <c r="AC68" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="O71" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P71" s="2" t="inlineStr">
@@ -8922,7 +8922,7 @@
       </c>
       <c r="AC71" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9150,17 +9150,17 @@
       </c>
       <c r="AA73" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB73" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC73" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9265,17 +9265,17 @@
       </c>
       <c r="AA74" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB74" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9379,22 +9379,22 @@
       </c>
       <c r="Z75" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="AC85" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -10745,12 +10745,12 @@
       <c r="K87" s="2" t="inlineStr"/>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±4分钟</t>
+          <t>SHMAAS终点近站ETA直接确认，约±2分钟</t>
         </is>
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="N87" s="2" t="inlineStr">
@@ -10760,7 +10760,7 @@
       </c>
       <c r="O87" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:30</t>
         </is>
       </c>
       <c r="P87" s="2" t="inlineStr">
@@ -10814,7 +10814,7 @@
       </c>
       <c r="AC87" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>9/18</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10961,32 +10961,36 @@
       </c>
       <c r="F89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G89" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>108分钟</t>
         </is>
       </c>
       <c r="J89" s="2" t="inlineStr"/>
       <c r="K89" s="2" t="inlineStr"/>
       <c r="L89" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M89" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M89" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N89" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -10994,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11018,17 +11022,17 @@
       </c>
       <c r="W89" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X89" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y89" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z89" s="2" t="inlineStr">
@@ -11038,17 +11042,17 @@
       </c>
       <c r="AA89" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB89" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>89.8</t>
         </is>
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>12/18</t>
         </is>
       </c>
     </row>
@@ -11076,32 +11080,36 @@
       </c>
       <c r="F90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G90" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="I90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>94分钟</t>
         </is>
       </c>
       <c r="J90" s="2" t="inlineStr"/>
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M90" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M90" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N90" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11109,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11133,17 +11141,17 @@
       </c>
       <c r="W90" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X90" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y90" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z90" s="2" t="inlineStr">
@@ -11153,17 +11161,17 @@
       </c>
       <c r="AA90" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB90" s="2" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>89.5</t>
         </is>
       </c>
       <c r="AC90" s="2" t="inlineStr">
         <is>
-          <t>9/18</t>
+          <t>10/18</t>
         </is>
       </c>
     </row>
@@ -11224,7 +11232,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11306,32 +11314,36 @@
       </c>
       <c r="F92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>19:59</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
       <c r="K92" s="2" t="inlineStr"/>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M92" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M92" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N92" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -11339,7 +11351,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11363,37 +11375,37 @@
       </c>
       <c r="W92" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X92" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y92" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z92" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>86.5</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>10/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -11454,7 +11466,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11569,7 +11581,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11684,7 +11696,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11799,7 +11811,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11914,7 +11926,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12029,7 +12041,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12144,7 +12156,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:20</t>
+          <t>19:40</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12202,6 +12214,121 @@
         </is>
       </c>
     </row>
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr"/>
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>沪A35616D</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="E100" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G100" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J100" s="2" t="inlineStr"/>
+      <c r="K100" s="2" t="inlineStr"/>
+      <c r="L100" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr"/>
+      <c r="N100" s="2" t="inlineStr">
+        <is>
+          <t>06:01</t>
+        </is>
+      </c>
+      <c r="O100" s="2" t="inlineStr">
+        <is>
+          <t>19:40</t>
+        </is>
+      </c>
+      <c r="P100" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q100" s="2" t="inlineStr"/>
+      <c r="R100" s="2" t="inlineStr"/>
+      <c r="S100" s="2" t="inlineStr"/>
+      <c r="T100" s="2" t="inlineStr"/>
+      <c r="U100" s="2" t="inlineStr">
+        <is>
+          <t>20:40</t>
+        </is>
+      </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W100" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X100" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y100" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z100" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA100" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB100" s="2" t="inlineStr">
+        <is>
+          <t>86.5</t>
+        </is>
+      </c>
+      <c r="AC100" s="2" t="inlineStr">
+        <is>
+          <t>4/18</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC100"/>
+  <dimension ref="A1:AC102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1176,17 +1176,17 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1375,7 +1375,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AC8" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1648,7 +1648,7 @@
       </c>
       <c r="Z10" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA10" s="2" t="inlineStr">
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1847,7 +1847,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -1891,17 +1891,17 @@
       </c>
       <c r="AA12" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB12" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC12" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2010,12 +2010,12 @@
       </c>
       <c r="AA13" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
@@ -2204,7 +2204,7 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
@@ -2248,12 +2248,12 @@
       </c>
       <c r="AA15" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB15" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC15" s="2" t="inlineStr">
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
@@ -2676,7 +2676,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2720,17 +2720,17 @@
       </c>
       <c r="AA19" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB19" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC19" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -2849,7 +2849,7 @@
       </c>
       <c r="AC20" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3271,7 +3271,7 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
@@ -3390,7 +3390,7 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="AC25" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3544,17 +3544,17 @@
       </c>
       <c r="Z26" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3901,7 +3901,7 @@
       </c>
       <c r="Z29" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA29" s="2" t="inlineStr">
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4025,12 +4025,12 @@
       </c>
       <c r="AA30" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -4144,17 +4144,17 @@
       </c>
       <c r="AA31" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB31" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC31" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -4630,7 +4630,7 @@
       </c>
       <c r="AC35" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -5060,7 +5060,7 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
@@ -5114,7 +5114,7 @@
       </c>
       <c r="AC39" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5469,12 +5469,12 @@
       </c>
       <c r="AA42" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="O43" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P43" s="2" t="inlineStr">
@@ -5588,17 +5588,17 @@
       </c>
       <c r="AA43" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB43" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC43" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -5955,7 +5955,7 @@
       </c>
       <c r="AC46" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -6139,7 +6139,7 @@
       </c>
       <c r="O48" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P48" s="2" t="inlineStr">
@@ -6258,7 +6258,7 @@
       </c>
       <c r="O49" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P49" s="2" t="inlineStr">
@@ -6312,7 +6312,7 @@
       </c>
       <c r="AC49" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6540,12 +6540,12 @@
       </c>
       <c r="AA51" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
@@ -6615,7 +6615,7 @@
       </c>
       <c r="O52" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P52" s="2" t="inlineStr">
@@ -6659,17 +6659,17 @@
       </c>
       <c r="AA52" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB52" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC52" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="AC55" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -7210,7 +7210,7 @@
       </c>
       <c r="O57" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P57" s="2" t="inlineStr">
@@ -7329,7 +7329,7 @@
       </c>
       <c r="O58" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P58" s="2" t="inlineStr">
@@ -7383,7 +7383,7 @@
       </c>
       <c r="AC58" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7730,12 +7730,12 @@
       </c>
       <c r="AA61" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
@@ -7805,7 +7805,7 @@
       </c>
       <c r="O62" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P62" s="2" t="inlineStr">
@@ -7849,17 +7849,17 @@
       </c>
       <c r="AA62" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB62" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC62" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7963,17 +7963,17 @@
       </c>
       <c r="Z63" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8043,7 +8043,7 @@
       </c>
       <c r="O64" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P64" s="2" t="inlineStr">
@@ -8087,12 +8087,12 @@
       </c>
       <c r="AA64" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB64" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC64" s="2" t="inlineStr">
@@ -8158,7 +8158,7 @@
       </c>
       <c r="O65" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P65" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="AA65" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB65" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC65" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8312,7 +8312,7 @@
       </c>
       <c r="Z66" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA66" s="2" t="inlineStr">
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8803,7 +8803,7 @@
       </c>
       <c r="AC70" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9106,7 +9106,7 @@
       </c>
       <c r="O73" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P73" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="O74" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P74" s="2" t="inlineStr">
@@ -9275,7 +9275,7 @@
       </c>
       <c r="AC74" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9389,7 +9389,7 @@
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
@@ -9578,7 +9578,7 @@
       </c>
       <c r="O77" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P77" s="2" t="inlineStr">
@@ -9622,12 +9622,12 @@
       </c>
       <c r="AA77" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB77" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC77" s="2" t="inlineStr">
@@ -9697,7 +9697,7 @@
       </c>
       <c r="O78" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P78" s="2" t="inlineStr">
@@ -9741,17 +9741,17 @@
       </c>
       <c r="AA78" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB78" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC78" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -9812,7 +9812,7 @@
       </c>
       <c r="O79" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P79" s="2" t="inlineStr">
@@ -9856,17 +9856,17 @@
       </c>
       <c r="AA79" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB79" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC79" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>14/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10089,17 +10089,17 @@
       </c>
       <c r="Z81" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10213,12 +10213,12 @@
       </c>
       <c r="AA82" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10327,7 +10327,7 @@
       </c>
       <c r="Z83" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA83" s="2" t="inlineStr">
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10695,7 +10695,7 @@
       </c>
       <c r="AC86" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>7/18</t>
         </is>
       </c>
     </row>
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10998,7 +10998,7 @@
       </c>
       <c r="O89" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P89" s="2" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="AC89" s="2" t="inlineStr">
         <is>
-          <t>12/18</t>
+          <t>13/18</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       <c r="K90" s="2" t="inlineStr"/>
       <c r="L90" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N90" s="2" t="inlineStr">
@@ -11117,7 +11117,7 @@
       </c>
       <c r="O90" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="P90" s="2" t="inlineStr">
@@ -11199,32 +11199,36 @@
       </c>
       <c r="F91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G91" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:05</t>
         </is>
       </c>
       <c r="I91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>90分钟</t>
         </is>
       </c>
       <c r="J91" s="2" t="inlineStr"/>
       <c r="K91" s="2" t="inlineStr"/>
       <c r="L91" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M91" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M91" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N91" s="2" t="inlineStr">
         <is>
           <t>07:20</t>
@@ -11232,7 +11236,7 @@
       </c>
       <c r="O91" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="P91" s="2" t="inlineStr">
@@ -11256,17 +11260,17 @@
       </c>
       <c r="W91" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X91" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y91" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z91" s="2" t="inlineStr">
@@ -11276,12 +11280,12 @@
       </c>
       <c r="AA91" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB91" s="2" t="inlineStr">
         <is>
-          <t>88.3</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="AC91" s="2" t="inlineStr">
@@ -11324,12 +11328,12 @@
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>19:59</t>
+          <t>19:58</t>
         </is>
       </c>
       <c r="I92" s="2" t="inlineStr">
         <is>
-          <t>79分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J92" s="2" t="inlineStr"/>
@@ -11351,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11400,7 +11404,7 @@
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
@@ -11433,32 +11437,36 @@
       </c>
       <c r="F93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G93" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:22</t>
         </is>
       </c>
       <c r="I93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>82分钟</t>
         </is>
       </c>
       <c r="J93" s="2" t="inlineStr"/>
       <c r="K93" s="2" t="inlineStr"/>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M93" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M93" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N93" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11466,7 +11474,7 @@
       </c>
       <c r="O93" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="P93" s="2" t="inlineStr">
@@ -11490,17 +11498,17 @@
       </c>
       <c r="W93" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X93" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y93" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z93" s="2" t="inlineStr">
@@ -11510,17 +11518,17 @@
       </c>
       <c r="AA93" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AB93" s="2" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AC93" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>14/18</t>
         </is>
       </c>
     </row>
@@ -11548,32 +11556,36 @@
       </c>
       <c r="F94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G94" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:31</t>
         </is>
       </c>
       <c r="I94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>86分钟</t>
         </is>
       </c>
       <c r="J94" s="2" t="inlineStr"/>
       <c r="K94" s="2" t="inlineStr"/>
       <c r="L94" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M94" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M94" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N94" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11581,7 +11593,7 @@
       </c>
       <c r="O94" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P94" s="2" t="inlineStr">
@@ -11605,17 +11617,17 @@
       </c>
       <c r="W94" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X94" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y94" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z94" s="2" t="inlineStr">
@@ -11625,17 +11637,17 @@
       </c>
       <c r="AA94" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AB94" s="2" t="inlineStr">
         <is>
-          <t>90.4</t>
+          <t>89.7</t>
         </is>
       </c>
       <c r="AC94" s="2" t="inlineStr">
         <is>
-          <t>13/18</t>
+          <t>11/18</t>
         </is>
       </c>
     </row>
@@ -11663,32 +11675,36 @@
       </c>
       <c r="F95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G95" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:46</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M95" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M95" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N95" s="2" t="inlineStr">
         <is>
           <t>07:01</t>
@@ -11696,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11720,17 +11736,17 @@
       </c>
       <c r="W95" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X95" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y95" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z95" s="2" t="inlineStr">
@@ -11740,12 +11756,12 @@
       </c>
       <c r="AA95" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>88.0</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
@@ -11778,32 +11794,36 @@
       </c>
       <c r="F96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G96" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>20:58</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>88分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M96" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M96" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N96" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -11811,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11835,32 +11855,32 @@
       </c>
       <c r="W96" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X96" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y96" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z96" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>102.0</t>
+          <t>98.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -11926,7 +11946,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -12041,7 +12061,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12080,7 +12100,7 @@
       </c>
       <c r="Z98" s="2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AA98" s="2" t="inlineStr">
@@ -12156,7 +12176,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12271,7 +12291,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>19:40</t>
+          <t>20:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12320,12 +12340,242 @@
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>86.5</t>
+          <t>86.2</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
           <t>4/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr"/>
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>沪A56630D</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="E101" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G101" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J101" s="2" t="inlineStr"/>
+      <c r="K101" s="2" t="inlineStr"/>
+      <c r="L101" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr"/>
+      <c r="N101" s="2" t="inlineStr">
+        <is>
+          <t>06:20</t>
+        </is>
+      </c>
+      <c r="O101" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P101" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q101" s="2" t="inlineStr"/>
+      <c r="R101" s="2" t="inlineStr"/>
+      <c r="S101" s="2" t="inlineStr"/>
+      <c r="T101" s="2" t="inlineStr"/>
+      <c r="U101" s="2" t="inlineStr">
+        <is>
+          <t>21:10</t>
+        </is>
+      </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W101" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X101" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y101" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z101" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA101" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB101" s="2" t="inlineStr">
+        <is>
+          <t>98.5</t>
+        </is>
+      </c>
+      <c r="AC101" s="2" t="inlineStr">
+        <is>
+          <t>18/18</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr"/>
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>沪A51173D</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>锦带路迎春路（浦东新区办公中心）</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="E102" s="2" t="inlineStr">
+        <is>
+          <t>港城路地铁站</t>
+        </is>
+      </c>
+      <c r="F102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="G102" s="2" t="inlineStr">
+        <is>
+          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+        </is>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="J102" s="2" t="inlineStr"/>
+      <c r="K102" s="2" t="inlineStr"/>
+      <c r="L102" s="2" t="inlineStr">
+        <is>
+          <t>尚无满足±5分钟标准的终点ETA</t>
+        </is>
+      </c>
+      <c r="M102" s="2" t="inlineStr"/>
+      <c r="N102" s="2" t="inlineStr">
+        <is>
+          <t>06:50</t>
+        </is>
+      </c>
+      <c r="O102" s="2" t="inlineStr">
+        <is>
+          <t>20:20</t>
+        </is>
+      </c>
+      <c r="P102" s="2" t="inlineStr">
+        <is>
+          <t>SHMAAS</t>
+        </is>
+      </c>
+      <c r="Q102" s="2" t="inlineStr"/>
+      <c r="R102" s="2" t="inlineStr"/>
+      <c r="S102" s="2" t="inlineStr"/>
+      <c r="T102" s="2" t="inlineStr"/>
+      <c r="U102" s="2" t="inlineStr">
+        <is>
+          <t>21:40</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>计划发车</t>
+        </is>
+      </c>
+      <c r="W102" s="2" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="X102" s="2" t="inlineStr">
+        <is>
+          <t>待确认</t>
+        </is>
+      </c>
+      <c r="Y102" s="2" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+      <c r="Z102" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AA102" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB102" s="2" t="inlineStr">
+        <is>
+          <t>96.3</t>
+        </is>
+      </c>
+      <c r="AC102" s="2" t="inlineStr">
+        <is>
+          <t>16/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -709,17 +709,17 @@
       </c>
       <c r="AA2" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB2" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -1256,7 +1256,7 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
@@ -1300,12 +1300,12 @@
       </c>
       <c r="AA7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB7" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC7" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="AC9" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -1653,17 +1653,17 @@
       </c>
       <c r="AA10" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB10" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC10" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1772,12 +1772,12 @@
       </c>
       <c r="AA11" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB11" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC11" s="2" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -2015,12 +2015,12 @@
       </c>
       <c r="AB13" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC13" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2377,7 @@
       </c>
       <c r="AC16" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -2492,7 +2492,7 @@
       </c>
       <c r="AC17" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -2601,17 +2601,17 @@
       </c>
       <c r="AA18" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB18" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC18" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="AC22" s="2" t="inlineStr">
         <is>
-          <t>17/18</t>
+          <t>18/18</t>
         </is>
       </c>
     </row>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -3196,12 +3196,12 @@
       </c>
       <c r="AA23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB23" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC23" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3554,12 +3554,12 @@
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -3678,7 +3678,7 @@
       </c>
       <c r="AC27" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3787,12 +3787,12 @@
       </c>
       <c r="AA28" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB28" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC28" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -3906,17 +3906,17 @@
       </c>
       <c r="AA29" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB29" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC29" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -3981,7 +3981,7 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="AB30" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC30" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -4392,7 +4392,7 @@
       </c>
       <c r="AC33" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -4511,7 +4511,7 @@
       </c>
       <c r="AC34" s="2" t="inlineStr">
         <is>
-          <t>3/18</t>
+          <t>4/18</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4929,7 @@
       </c>
       <c r="O38" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P38" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="AA38" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB38" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC38" s="2" t="inlineStr">
@@ -5233,7 +5233,7 @@
       </c>
       <c r="AC40" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5294,7 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
@@ -5350,12 +5350,12 @@
       </c>
       <c r="AA41" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB41" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC41" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
@@ -5474,12 +5474,12 @@
       </c>
       <c r="AB42" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC42" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="AC44" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="AC50" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
       </c>
       <c r="O51" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P51" s="2" t="inlineStr">
@@ -6545,12 +6545,12 @@
       </c>
       <c r="AB51" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC51" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="AC53" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7492,17 +7492,17 @@
       </c>
       <c r="AA59" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB59" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC59" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -7621,7 +7621,7 @@
       </c>
       <c r="AC60" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -7686,7 +7686,7 @@
       </c>
       <c r="O61" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P61" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="AB61" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC61" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7973,12 +7973,12 @@
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -8317,17 +8317,17 @@
       </c>
       <c r="AA66" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB66" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC66" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -8446,7 +8446,7 @@
       </c>
       <c r="AC67" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -8630,7 +8630,7 @@
       </c>
       <c r="O69" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P69" s="2" t="inlineStr">
@@ -8674,12 +8674,12 @@
       </c>
       <c r="AA69" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB69" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC69" s="2" t="inlineStr">
@@ -8987,7 +8987,7 @@
       </c>
       <c r="O72" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P72" s="2" t="inlineStr">
@@ -9031,12 +9031,12 @@
       </c>
       <c r="AA72" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB72" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC72" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -9384,17 +9384,17 @@
       </c>
       <c r="AA75" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB75" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC75" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -9513,7 +9513,7 @@
       </c>
       <c r="AC76" s="2" t="inlineStr">
         <is>
-          <t>5/18</t>
+          <t>6/18</t>
         </is>
       </c>
     </row>
@@ -9985,7 +9985,7 @@
       </c>
       <c r="AC80" s="2" t="inlineStr">
         <is>
-          <t>15/18</t>
+          <t>16/18</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10099,12 +10099,12 @@
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
       </c>
       <c r="O82" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P82" s="2" t="inlineStr">
@@ -10218,12 +10218,12 @@
       </c>
       <c r="AB82" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC82" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -10332,17 +10332,17 @@
       </c>
       <c r="AA83" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB83" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC83" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -10403,7 +10403,7 @@
       </c>
       <c r="O84" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P84" s="2" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="AA84" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB84" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC84" s="2" t="inlineStr">
@@ -10879,7 +10879,7 @@
       </c>
       <c r="O88" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P88" s="2" t="inlineStr">
@@ -10923,12 +10923,12 @@
       </c>
       <c r="AA88" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB88" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC88" s="2" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11399,17 +11399,17 @@
       </c>
       <c r="AA92" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB92" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC92" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -11685,24 +11685,24 @@
       </c>
       <c r="H95" s="2" t="inlineStr">
         <is>
-          <t>20:46</t>
+          <t>20:43</t>
         </is>
       </c>
       <c r="I95" s="2" t="inlineStr">
         <is>
-          <t>81分钟</t>
+          <t>78分钟</t>
         </is>
       </c>
       <c r="J95" s="2" t="inlineStr"/>
       <c r="K95" s="2" t="inlineStr"/>
       <c r="L95" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N95" s="2" t="inlineStr">
@@ -11712,7 +11712,7 @@
       </c>
       <c r="O95" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>20:40</t>
         </is>
       </c>
       <c r="P95" s="2" t="inlineStr">
@@ -11761,12 +11761,12 @@
       </c>
       <c r="AB95" s="2" t="inlineStr">
         <is>
-          <t>87.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="AC95" s="2" t="inlineStr">
         <is>
-          <t>6/18</t>
+          <t>5/18</t>
         </is>
       </c>
     </row>
@@ -11804,24 +11804,24 @@
       </c>
       <c r="H96" s="2" t="inlineStr">
         <is>
-          <t>20:58</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="I96" s="2" t="inlineStr">
         <is>
-          <t>88分钟</t>
+          <t>84分钟</t>
         </is>
       </c>
       <c r="J96" s="2" t="inlineStr"/>
       <c r="K96" s="2" t="inlineStr"/>
       <c r="L96" s="2" t="inlineStr">
         <is>
-          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
         </is>
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11880,12 +11880,12 @@
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -11913,32 +11913,36 @@
       </c>
       <c r="F97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G97" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:09</t>
         </is>
       </c>
       <c r="I97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>79分钟</t>
         </is>
       </c>
       <c r="J97" s="2" t="inlineStr"/>
       <c r="K97" s="2" t="inlineStr"/>
       <c r="L97" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M97" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M97" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N97" s="2" t="inlineStr">
         <is>
           <t>06:30</t>
@@ -11946,7 +11950,7 @@
       </c>
       <c r="O97" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:01</t>
         </is>
       </c>
       <c r="P97" s="2" t="inlineStr">
@@ -11970,17 +11974,17 @@
       </c>
       <c r="W97" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X97" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y97" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z97" s="2" t="inlineStr">
@@ -11990,12 +11994,12 @@
       </c>
       <c r="AA97" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB97" s="2" t="inlineStr">
         <is>
-          <t>84.3</t>
+          <t>83.0</t>
         </is>
       </c>
       <c r="AC97" s="2" t="inlineStr">
@@ -12028,32 +12032,36 @@
       </c>
       <c r="F98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G98" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:12</t>
         </is>
       </c>
       <c r="I98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>74分钟</t>
         </is>
       </c>
       <c r="J98" s="2" t="inlineStr"/>
       <c r="K98" s="2" t="inlineStr"/>
       <c r="L98" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M98" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M98" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N98" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12061,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12085,17 +12093,17 @@
       </c>
       <c r="W98" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X98" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y98" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z98" s="2" t="inlineStr">
@@ -12105,17 +12113,17 @@
       </c>
       <c r="AA98" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB98" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC98" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>
@@ -12143,32 +12151,36 @@
       </c>
       <c r="F99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G99" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>21:36</t>
         </is>
       </c>
       <c r="I99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J99" s="2" t="inlineStr"/>
       <c r="K99" s="2" t="inlineStr"/>
       <c r="L99" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M99" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M99" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N99" s="2" t="inlineStr">
         <is>
           <t>06:50</t>
@@ -12176,7 +12188,7 @@
       </c>
       <c r="O99" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P99" s="2" t="inlineStr">
@@ -12200,17 +12212,17 @@
       </c>
       <c r="W99" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X99" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y99" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z99" s="2" t="inlineStr">
@@ -12220,12 +12232,12 @@
       </c>
       <c r="AA99" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB99" s="2" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>84.4</t>
         </is>
       </c>
       <c r="AC99" s="2" t="inlineStr">
@@ -12258,32 +12270,36 @@
       </c>
       <c r="F100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G100" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:00</t>
         </is>
       </c>
       <c r="I100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>80分钟</t>
         </is>
       </c>
       <c r="J100" s="2" t="inlineStr"/>
       <c r="K100" s="2" t="inlineStr"/>
       <c r="L100" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M100" s="2" t="inlineStr"/>
+          <t>SHMAAS多次终点ETA一致估算，约±3分钟</t>
+        </is>
+      </c>
+      <c r="M100" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="N100" s="2" t="inlineStr">
         <is>
           <t>06:01</t>
@@ -12291,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12315,17 +12331,17 @@
       </c>
       <c r="W100" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X100" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y100" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z100" s="2" t="inlineStr">
@@ -12335,17 +12351,17 @@
       </c>
       <c r="AA100" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB100" s="2" t="inlineStr">
         <is>
-          <t>86.2</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="AC100" s="2" t="inlineStr">
         <is>
-          <t>4/18</t>
+          <t>3/18</t>
         </is>
       </c>
     </row>
@@ -12406,7 +12422,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12455,12 +12471,12 @@
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>98.5</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
         <is>
-          <t>18/18</t>
+          <t>17/18</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12537,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>20:20</t>
+          <t>21:20</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
@@ -12565,17 +12581,17 @@
       </c>
       <c r="AA102" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AB102" s="2" t="inlineStr">
         <is>
-          <t>96.3</t>
+          <t>90.8</t>
         </is>
       </c>
       <c r="AC102" s="2" t="inlineStr">
         <is>
-          <t>16/18</t>
+          <t>15/18</t>
         </is>
       </c>
     </row>

--- a/data/export/2026-10-14-浦东78路.xlsx
+++ b/data/export/2026-10-14-浦东78路.xlsx
@@ -665,7 +665,7 @@
       </c>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P2" s="2" t="inlineStr">
@@ -1137,7 +1137,7 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
@@ -1181,12 +1181,12 @@
       </c>
       <c r="AA6" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB6" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC6" s="2" t="inlineStr">
@@ -1609,7 +1609,7 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
@@ -2557,7 +2557,7 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
@@ -3505,7 +3505,7 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="AA26" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB26" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC26" s="2" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
@@ -7448,7 +7448,7 @@
       </c>
       <c r="O59" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P59" s="2" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="O63" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P63" s="2" t="inlineStr">
@@ -7968,12 +7968,12 @@
       </c>
       <c r="AA63" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB63" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC63" s="2" t="inlineStr">
@@ -8273,7 +8273,7 @@
       </c>
       <c r="O66" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P66" s="2" t="inlineStr">
@@ -9340,7 +9340,7 @@
       </c>
       <c r="O75" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P75" s="2" t="inlineStr">
@@ -10050,7 +10050,7 @@
       </c>
       <c r="O81" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P81" s="2" t="inlineStr">
@@ -10094,12 +10094,12 @@
       </c>
       <c r="AA81" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB81" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC81" s="2" t="inlineStr">
@@ -10288,7 +10288,7 @@
       </c>
       <c r="O83" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P83" s="2" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="O92" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P92" s="2" t="inlineStr">
@@ -11831,7 +11831,7 @@
       </c>
       <c r="O96" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P96" s="2" t="inlineStr">
@@ -11875,12 +11875,12 @@
       </c>
       <c r="AA96" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB96" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC96" s="2" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="O98" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P98" s="2" t="inlineStr">
@@ -12307,7 +12307,7 @@
       </c>
       <c r="O100" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>21:50</t>
         </is>
       </c>
       <c r="P100" s="2" t="inlineStr">
@@ -12389,32 +12389,36 @@
       </c>
       <c r="F101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>全程车</t>
         </is>
       </c>
       <c r="G101" s="2" t="inlineStr">
         <is>
-          <t>既无可靠终点到达证据，也未形成反向≥2站物理推进证据或可靠时空矛盾</t>
+          <t>已取得可靠同向线路终点ETA，按全程车保护</t>
         </is>
       </c>
       <c r="H101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>22:31</t>
         </is>
       </c>
       <c r="I101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>81分钟</t>
         </is>
       </c>
       <c r="J101" s="2" t="inlineStr"/>
       <c r="K101" s="2" t="inlineStr"/>
       <c r="L101" s="2" t="inlineStr">
         <is>
-          <t>尚无满足±5分钟标准的终点ETA</t>
-        </is>
-      </c>
-      <c r="M101" s="2" t="inlineStr"/>
+          <t>SHMAAS终点ETA近站估算，约±5分钟</t>
+        </is>
+      </c>
+      <c r="M101" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
       <c r="N101" s="2" t="inlineStr">
         <is>
           <t>06:20</t>
@@ -12422,7 +12426,7 @@
       </c>
       <c r="O101" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P101" s="2" t="inlineStr">
@@ -12446,17 +12450,17 @@
       </c>
       <c r="W101" s="2" t="inlineStr">
         <is>
-          <t>D</t>
+          <t>A</t>
         </is>
       </c>
       <c r="X101" s="2" t="inlineStr">
         <is>
-          <t>待确认</t>
+          <t>终点ETA确认/一致估算</t>
         </is>
       </c>
       <c r="Y101" s="2" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="Z101" s="2" t="inlineStr">
@@ -12466,12 +12470,12 @@
       </c>
       <c r="AA101" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AB101" s="2" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.2</t>
         </is>
       </c>
       <c r="AC101" s="2" t="inlineStr">
@@ -12537,7 +12541,7 @@
       </c>
       <c r="O102" s="2" t="inlineStr">
         <is>
-          <t>21:20</t>
+          <t>22:27</t>
         </is>
       </c>
       <c r="P102" s="2" t="inlineStr">
